--- a/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
+++ b/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="98">
   <si>
     <t>Michael the International Baker</t>
   </si>
@@ -55,10 +55,13 @@
     <t>The Turbanator</t>
   </si>
   <si>
-    <t>0-1-0</t>
-  </si>
-  <si>
-    <t>1-0-0</t>
+    <t>0-2-0</t>
+  </si>
+  <si>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -118,6 +121,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -139,36 +145,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Marvin Ta</t>
+  </si>
+  <si>
     <t>Anthony Rizzo</t>
   </si>
   <si>
+    <t>Maulin Patel</t>
+  </si>
+  <si>
+    <t>Chris Carbone</t>
+  </si>
+  <si>
     <t>Alyssa Ianovale</t>
   </si>
   <si>
-    <t>Marvin Ta</t>
+    <t>Victor Rojas</t>
+  </si>
+  <si>
+    <t>Robbie Wilston</t>
+  </si>
+  <si>
+    <t>Prahlad Singh</t>
   </si>
   <si>
     <t>Kermelos Woldeyes</t>
   </si>
   <si>
-    <t>Robbie Wilston</t>
-  </si>
-  <si>
-    <t>Maulin Patel</t>
-  </si>
-  <si>
-    <t>Chris Carbone</t>
-  </si>
-  <si>
-    <t>Victor Rojas</t>
-  </si>
-  <si>
     <t>Bridget Cashel</t>
   </si>
   <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -193,51 +199,51 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>10.6-3.3-0.1</t>
-  </si>
-  <si>
-    <t>9.4-4.6-0.1</t>
-  </si>
-  <si>
-    <t>9.3-4.6-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>7.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.3-0.1</t>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>9.7-4.2-0.1</t>
+  </si>
+  <si>
+    <t>8.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>8.2-5.7-0.1</t>
+  </si>
+  <si>
+    <t>7.7-6.2-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
   </si>
   <si>
     <t>5.8-8.1-0.1</t>
   </si>
   <si>
-    <t>5.6-8.3-0.1</t>
+    <t>5.6-8.4-0.1</t>
+  </si>
+  <si>
+    <t>4.9-9.0-0.1</t>
   </si>
   <si>
     <t>4.3-9.6-0.1</t>
   </si>
   <si>
-    <t>1.8-12.1-0.1</t>
-  </si>
-  <si>
-    <t>11-3</t>
-  </si>
-  <si>
     <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
   </si>
   <si>
+    <t>8-6</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
@@ -250,9 +256,6 @@
     <t>4-10</t>
   </si>
   <si>
-    <t>1-13</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -262,7 +265,37 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↓7</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -684,7 +717,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -719,13 +752,13 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -734,13 +767,13 @@
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
         <v>11</v>
@@ -754,13 +787,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -769,13 +802,13 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
         <v>11</v>
@@ -786,16 +819,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -804,16 +837,16 @@
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -821,16 +854,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -839,16 +872,16 @@
         <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -856,34 +889,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -894,13 +927,13 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -909,16 +942,16 @@
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -929,13 +962,13 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -999,13 +1032,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
@@ -1033,30 +1066,56 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>-2</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1071,13 +1130,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1088,7 +1147,7 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1102,10 +1161,10 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1113,13 +1172,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1127,10 +1186,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1141,10 +1200,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -1155,10 +1214,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -1169,13 +1228,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1186,7 +1245,7 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1197,10 +1256,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1211,13 +1270,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1232,16 +1291,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1249,13 +1308,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -1266,16 +1325,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D3">
-        <v>-0.09999999999999998</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1283,16 +1342,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D4">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1300,13 +1359,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1317,16 +1376,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1334,13 +1393,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="D7">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1351,16 +1410,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D8">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1368,13 +1427,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1385,16 +1444,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1402,13 +1461,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1426,116 +1485,116 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>53.3</v>
+      </c>
+      <c r="C2">
+        <v>20.5</v>
+      </c>
+      <c r="D2">
+        <v>12.4</v>
+      </c>
+      <c r="E2">
         <v>7</v>
       </c>
-      <c r="B2">
-        <v>54.5</v>
-      </c>
-      <c r="C2">
-        <v>22.2</v>
-      </c>
-      <c r="D2">
-        <v>12.3</v>
-      </c>
-      <c r="E2">
-        <v>6.8</v>
-      </c>
       <c r="F2">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>10.2</v>
+      </c>
+      <c r="C3">
+        <v>19.3</v>
+      </c>
+      <c r="D3">
+        <v>18.5</v>
+      </c>
+      <c r="E3">
+        <v>15.5</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
         <v>9</v>
       </c>
-      <c r="B3">
-        <v>15.5</v>
-      </c>
-      <c r="C3">
-        <v>24.3</v>
-      </c>
-      <c r="D3">
-        <v>23.2</v>
-      </c>
-      <c r="E3">
-        <v>20.3</v>
-      </c>
-      <c r="F3">
-        <v>9.9</v>
-      </c>
-      <c r="G3">
-        <v>4.2</v>
-      </c>
       <c r="H3">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L3">
-        <v>97.40000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1543,37 +1602,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>11.2</v>
       </c>
       <c r="C4">
-        <v>23.9</v>
+        <v>17.2</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>14.8</v>
       </c>
       <c r="E4">
-        <v>21.1</v>
+        <v>18.7</v>
       </c>
       <c r="F4">
-        <v>9.1</v>
+        <v>15.2</v>
       </c>
       <c r="G4">
-        <v>3.8</v>
+        <v>10.2</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="I4">
+        <v>4.1</v>
+      </c>
+      <c r="J4">
+        <v>1.7</v>
+      </c>
+      <c r="K4">
         <v>0.8</v>
       </c>
-      <c r="J4">
-        <v>0.2</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
       <c r="L4">
-        <v>96.90000000000001</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1581,265 +1640,265 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>14.3</v>
+        <v>10.2</v>
       </c>
       <c r="C5">
-        <v>22.3</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>23.9</v>
+        <v>16.3</v>
       </c>
       <c r="E5">
-        <v>18.4</v>
+        <v>17.2</v>
       </c>
       <c r="F5">
-        <v>11.7</v>
+        <v>14.4</v>
       </c>
       <c r="G5">
-        <v>5.3</v>
+        <v>13.1</v>
       </c>
       <c r="H5">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L5">
-        <v>95.90000000000001</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>0.3</v>
+        <v>8.9</v>
       </c>
       <c r="C6">
-        <v>3.1</v>
+        <v>12.4</v>
       </c>
       <c r="D6">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>14.2</v>
+        <v>16.3</v>
       </c>
       <c r="F6">
-        <v>23.4</v>
+        <v>13.9</v>
       </c>
       <c r="G6">
-        <v>22.8</v>
+        <v>10.5</v>
       </c>
       <c r="H6">
-        <v>16.4</v>
+        <v>10.3</v>
       </c>
       <c r="I6">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="J6">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="L6">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>4.6</v>
       </c>
       <c r="C7">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>5.3</v>
+        <v>11.4</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>12.1</v>
       </c>
       <c r="F7">
-        <v>18.3</v>
+        <v>15.5</v>
       </c>
       <c r="G7">
-        <v>22.5</v>
+        <v>14.8</v>
       </c>
       <c r="H7">
-        <v>20.1</v>
+        <v>12.4</v>
       </c>
       <c r="I7">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="J7">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="K7">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="L7">
-        <v>57.3</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C8">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E8">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="F8">
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>18.3</v>
+        <v>16.1</v>
       </c>
       <c r="H8">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="I8">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="J8">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="K8">
-        <v>2.1</v>
+        <v>8.9</v>
       </c>
       <c r="L8">
-        <v>39.8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="C9">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="D9">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="F9">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="G9">
-        <v>16</v>
+        <v>11.9</v>
       </c>
       <c r="H9">
-        <v>23.7</v>
+        <v>15.4</v>
       </c>
       <c r="I9">
-        <v>27.1</v>
+        <v>16.9</v>
       </c>
       <c r="J9">
-        <v>15.2</v>
+        <v>19</v>
       </c>
       <c r="K9">
-        <v>2.4</v>
+        <v>15.5</v>
       </c>
       <c r="L9">
-        <v>31.6</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E10">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="F10">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H10">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="I10">
-        <v>22.6</v>
+        <v>18.2</v>
       </c>
       <c r="J10">
-        <v>46.5</v>
+        <v>24.9</v>
       </c>
       <c r="K10">
-        <v>9.1</v>
+        <v>30.7</v>
       </c>
       <c r="L10">
-        <v>10.2</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="G11">
-        <v>0.2</v>
+        <v>5.8</v>
       </c>
       <c r="H11">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="I11">
-        <v>1.9</v>
+        <v>15.4</v>
       </c>
       <c r="J11">
-        <v>11.9</v>
+        <v>27.1</v>
       </c>
       <c r="K11">
-        <v>85.59999999999999</v>
+        <v>38.9</v>
       </c>
       <c r="L11">
-        <v>0.2</v>
+        <v>10.9</v>
       </c>
     </row>
   </sheetData>
@@ -1849,125 +1908,158 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>99.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C2">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>98.5</v>
+      </c>
+      <c r="D2">
+        <v>98.59999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>37.9</v>
+      </c>
+      <c r="C3">
+        <v>90.2</v>
+      </c>
+      <c r="D3">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="C3">
-        <v>97.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B4">
-        <v>97.7</v>
+        <v>97.2</v>
       </c>
       <c r="C4">
-        <v>97.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="D4">
+        <v>86.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>98.8</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="C5">
-        <v>96.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>88.5</v>
+      </c>
+      <c r="D5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>69.5</v>
+        <v>99.8</v>
       </c>
       <c r="C6">
-        <v>73.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>80.7</v>
+      </c>
+      <c r="D6">
+        <v>79.90000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="C7">
+        <v>73.7</v>
+      </c>
+      <c r="D7">
+        <v>71.89999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>8.799999999999999</v>
+      </c>
+      <c r="C8">
+        <v>31.2</v>
+      </c>
+      <c r="D8">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>0.1</v>
+      </c>
+      <c r="C9">
+        <v>27.1</v>
+      </c>
+      <c r="D9">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>56.39999999999999</v>
-      </c>
-      <c r="C7">
-        <v>54.40000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>38.1</v>
-      </c>
-      <c r="C8">
-        <v>38.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
+      <c r="B10">
+        <v>57.8</v>
+      </c>
+      <c r="C10">
+        <v>14.7</v>
+      </c>
+      <c r="D10">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9">
-        <v>33.6</v>
-      </c>
-      <c r="C9">
-        <v>34.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>8.6</v>
-      </c>
-      <c r="C10">
-        <v>8.200000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>7.8</v>
+      </c>
+      <c r="D11">
+        <v>8.799999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1982,28 +2074,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2011,28 +2103,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>117.86</v>
+        <v>102.98</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>125.63</v>
+        <v>124.15</v>
       </c>
       <c r="G2">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2040,28 +2132,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>107</v>
+        <v>107.22</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>126.97</v>
+        <v>122.38</v>
       </c>
       <c r="G3">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2069,28 +2161,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>118.96</v>
+        <v>122.45</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>126.61</v>
+        <v>121.46</v>
       </c>
       <c r="G4">
-        <v>0.462</v>
+        <v>0.417</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2098,28 +2190,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>84.09999999999999</v>
+        <v>123.55</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>130.06</v>
+        <v>121.15</v>
       </c>
       <c r="G5">
-        <v>0.538</v>
+        <v>0.375</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2127,28 +2219,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>155.66</v>
+        <v>113.89</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>125.68</v>
+        <v>122.78</v>
       </c>
       <c r="G6">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2156,28 +2248,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>139.16</v>
+        <v>127.74</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
-        <v>122.35</v>
+        <v>120.05</v>
       </c>
       <c r="G7">
-        <v>0.462</v>
+        <v>0.542</v>
       </c>
       <c r="H7">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2185,28 +2277,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>140.4</v>
+        <v>128.97</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8">
-        <v>122.67</v>
+        <v>119.39</v>
       </c>
       <c r="G8">
-        <v>0.385</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2214,28 +2306,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>120.02</v>
+        <v>122.33</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>125.86</v>
+        <v>120.58</v>
       </c>
       <c r="G9">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-0.5</v>
+        <v>-1.4</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2243,28 +2335,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>126.56</v>
+        <v>113.63</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>121.14</v>
+        <v>120.77</v>
       </c>
       <c r="G10">
-        <v>0.538</v>
+        <v>0.583</v>
       </c>
       <c r="H10">
-        <v>-0.7</v>
+        <v>-1.6</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2272,28 +2364,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>141.2</v>
+        <v>146.89</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11">
-        <v>123.95</v>
+        <v>116.93</v>
       </c>
       <c r="G11">
-        <v>0.462</v>
+        <v>0.542</v>
       </c>
       <c r="H11">
-        <v>-0.9</v>
+        <v>-2.1</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2308,89 +2400,89 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>155.66</v>
+        <v>146.89</v>
       </c>
       <c r="E2">
-        <v>155.66</v>
+        <v>293.78</v>
       </c>
       <c r="F2">
-        <v>99.7</v>
+        <v>98.3</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3">
-        <v>141.2</v>
+        <v>127.74</v>
       </c>
       <c r="E3">
-        <v>141.2</v>
+        <v>255.48</v>
       </c>
       <c r="F3">
-        <v>97.39999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2398,28 +2490,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>140.4</v>
+        <v>123.55</v>
       </c>
       <c r="E4">
-        <v>140.4</v>
+        <v>247.1</v>
       </c>
       <c r="F4">
-        <v>96.89999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2427,202 +2519,202 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>139.16</v>
+        <v>122.45</v>
       </c>
       <c r="E5">
-        <v>139.16</v>
+        <v>244.9</v>
       </c>
       <c r="F5">
-        <v>95.89999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>126.56</v>
+        <v>128.97</v>
       </c>
       <c r="E6">
-        <v>126.56</v>
+        <v>257.94</v>
       </c>
       <c r="F6">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G6">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>118.96</v>
+        <v>122.33</v>
       </c>
       <c r="E7">
-        <v>118.96</v>
+        <v>244.66</v>
       </c>
       <c r="F7">
-        <v>57.3</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>120.02</v>
+        <v>113.89</v>
       </c>
       <c r="E8">
-        <v>120.02</v>
+        <v>227.78</v>
       </c>
       <c r="F8">
-        <v>39.8</v>
+        <v>34</v>
       </c>
       <c r="G8">
-        <v>2.1</v>
+        <v>8.9</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>117.86</v>
+        <v>113.63</v>
       </c>
       <c r="E9">
-        <v>117.86</v>
+        <v>227.26</v>
       </c>
       <c r="F9">
-        <v>31.6</v>
+        <v>33.2</v>
       </c>
       <c r="G9">
-        <v>2.4</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>107</v>
+        <v>102.98</v>
       </c>
       <c r="E10">
-        <v>107</v>
+        <v>205.96</v>
       </c>
       <c r="F10">
-        <v>10.2</v>
+        <v>14.2</v>
       </c>
       <c r="G10">
-        <v>9.1</v>
+        <v>30.7</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>84.09999999999999</v>
+        <v>107.22</v>
       </c>
       <c r="E11">
-        <v>84.09999999999999</v>
+        <v>214.44</v>
       </c>
       <c r="F11">
-        <v>0.2</v>
+        <v>10.9</v>
       </c>
       <c r="G11">
-        <v>85.59999999999999</v>
+        <v>38.9</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2637,19 +2729,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2657,19 +2749,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>0</v>
+      <c r="F2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2677,19 +2769,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2697,19 +2789,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
       <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2717,19 +2809,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2737,10 +2829,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2748,8 +2840,8 @@
       <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2757,19 +2849,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
-      <c r="F7">
-        <v>0</v>
+      <c r="F7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2777,19 +2869,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2797,19 +2889,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2817,19 +2909,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2837,19 +2929,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2859,125 +2951,158 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>-1</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B4">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>-2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>-4</v>
+      </c>
+      <c r="C8">
+        <v>-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>-1</v>
+      </c>
+      <c r="C9">
+        <v>-6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>-1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>-1</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
+      <c r="B10">
+        <v>-6</v>
+      </c>
+      <c r="C10">
+        <v>-8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
         <v>-4</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>-4</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11">
-        <v>-6</v>
-      </c>
       <c r="C11">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
+++ b/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
@@ -208,28 +208,28 @@
     <t>0-2</t>
   </si>
   <si>
-    <t>9.7-4.2-0.1</t>
-  </si>
-  <si>
-    <t>8.1-5.8-0.1</t>
+    <t>9.6-4.3-0.1</t>
   </si>
   <si>
     <t>8.2-5.7-0.1</t>
   </si>
   <si>
-    <t>7.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.1</t>
-  </si>
-  <si>
-    <t>5.6-8.4-0.1</t>
-  </si>
-  <si>
-    <t>4.9-9.0-0.1</t>
+    <t>8.3-5.6-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.2-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.8-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.5-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
   </si>
   <si>
     <t>4.3-9.6-0.1</t>
@@ -238,10 +238,10 @@
     <t>10-4</t>
   </si>
   <si>
+    <t>8-6</t>
+  </si>
+  <si>
     <t>9-5</t>
-  </si>
-  <si>
-    <t>8-6</t>
   </si>
   <si>
     <t>7-7</t>
@@ -1526,37 +1526,37 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>53.3</v>
+        <v>50.6</v>
       </c>
       <c r="C2">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="D2">
-        <v>12.4</v>
+        <v>11.1</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="F2">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
         <v>1.2</v>
       </c>
       <c r="I2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
-        <v>98.3</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1564,37 +1564,37 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="C3">
-        <v>19.3</v>
+        <v>18.2</v>
       </c>
       <c r="D3">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>15.5</v>
+        <v>16.7</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>12.6</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>11.1</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="L3">
-        <v>87.5</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1602,37 +1602,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>11.2</v>
+        <v>13.3</v>
       </c>
       <c r="C4">
-        <v>17.2</v>
+        <v>15.4</v>
       </c>
       <c r="D4">
-        <v>14.8</v>
+        <v>17.8</v>
       </c>
       <c r="E4">
-        <v>18.7</v>
+        <v>15.5</v>
       </c>
       <c r="F4">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
       <c r="G4">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K4">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="L4">
-        <v>87.3</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1640,37 +1640,37 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="D5">
+        <v>15.6</v>
+      </c>
+      <c r="E5">
         <v>16.3</v>
       </c>
-      <c r="E5">
-        <v>17.2</v>
-      </c>
       <c r="F5">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="G5">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="H5">
         <v>6.3</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J5">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="K5">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="L5">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1678,37 +1678,37 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>8.9</v>
+        <v>10.6</v>
       </c>
       <c r="C6">
-        <v>12.4</v>
+        <v>15.2</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="E6">
-        <v>16.3</v>
+        <v>13.8</v>
       </c>
       <c r="F6">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="H6">
-        <v>10.3</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J6">
         <v>3.6</v>
       </c>
       <c r="K6">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="L6">
-        <v>79</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1716,37 +1716,37 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D7">
-        <v>11.4</v>
+        <v>12.5</v>
       </c>
       <c r="E7">
-        <v>12.1</v>
+        <v>15.3</v>
       </c>
       <c r="F7">
-        <v>15.5</v>
+        <v>14.3</v>
       </c>
       <c r="G7">
         <v>14.8</v>
       </c>
       <c r="H7">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="I7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="K7">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="L7">
-        <v>69.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1754,37 +1754,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="D8">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E8">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>11.3</v>
       </c>
       <c r="G8">
-        <v>16.1</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="I8">
-        <v>21.5</v>
+        <v>19.3</v>
       </c>
       <c r="J8">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="K8">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="L8">
-        <v>34</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1792,37 +1792,37 @@
         <v>4</v>
       </c>
       <c r="B9">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="C9">
         <v>2.3</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="E9">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="F9">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="G9">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="H9">
-        <v>15.4</v>
+        <v>16.6</v>
       </c>
       <c r="I9">
-        <v>16.9</v>
+        <v>17.4</v>
       </c>
       <c r="J9">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="K9">
-        <v>15.5</v>
+        <v>19.3</v>
       </c>
       <c r="L9">
-        <v>33.2</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1830,37 +1830,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="E10">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>4</v>
       </c>
       <c r="G10">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="I10">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="J10">
-        <v>24.9</v>
+        <v>27.8</v>
       </c>
       <c r="K10">
-        <v>30.7</v>
+        <v>28.6</v>
       </c>
       <c r="L10">
-        <v>14.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1871,34 +1871,34 @@
         <v>0.1</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E11">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F11">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="G11">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="H11">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="I11">
-        <v>15.4</v>
+        <v>16.4</v>
       </c>
       <c r="J11">
-        <v>27.1</v>
+        <v>27.5</v>
       </c>
       <c r="K11">
-        <v>38.9</v>
+        <v>38.4</v>
       </c>
       <c r="L11">
-        <v>10.9</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -1927,13 +1927,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>67.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="C2">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D2">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1941,13 +1941,13 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>37.9</v>
+        <v>36.3</v>
       </c>
       <c r="C3">
-        <v>90.2</v>
+        <v>92.5</v>
       </c>
       <c r="D3">
-        <v>88.5</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1955,41 +1955,41 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>97.2</v>
+        <v>98.3</v>
       </c>
       <c r="C4">
-        <v>87.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D4">
-        <v>86.2</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>97.39999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C5">
-        <v>88.5</v>
+        <v>80.80000000000001</v>
       </c>
       <c r="D5">
-        <v>86</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>99.8</v>
+        <v>97.2</v>
       </c>
       <c r="C6">
-        <v>80.7</v>
+        <v>85.2</v>
       </c>
       <c r="D6">
-        <v>79.90000000000001</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1997,13 +1997,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="C7">
-        <v>73.7</v>
+        <v>70</v>
       </c>
       <c r="D7">
-        <v>71.89999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2011,13 +2011,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>8.799999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="C8">
-        <v>31.2</v>
+        <v>38.3</v>
       </c>
       <c r="D8">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2028,10 +2028,10 @@
         <v>0.1</v>
       </c>
       <c r="C9">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="D9">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2039,13 +2039,13 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>57.8</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="C10">
-        <v>14.7</v>
+        <v>11.9</v>
       </c>
       <c r="D10">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2053,13 +2053,13 @@
         <v>0</v>
       </c>
       <c r="B11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D11">
-        <v>8.799999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -2444,10 +2444,10 @@
         <v>293.78</v>
       </c>
       <c r="F2">
-        <v>98.3</v>
+        <v>98</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="s">
         <v>61</v>
@@ -2473,10 +2473,10 @@
         <v>255.48</v>
       </c>
       <c r="F3">
-        <v>87.5</v>
+        <v>88.7</v>
       </c>
       <c r="G3">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="s">
         <v>62</v>
@@ -2502,16 +2502,16 @@
         <v>247.1</v>
       </c>
       <c r="F4">
-        <v>87.3</v>
+        <v>87.2</v>
       </c>
       <c r="G4">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="s">
         <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2531,10 +2531,10 @@
         <v>244.9</v>
       </c>
       <c r="F5">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="G5">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="s">
         <v>62</v>
@@ -2560,16 +2560,16 @@
         <v>257.94</v>
       </c>
       <c r="F6">
-        <v>79</v>
+        <v>81.2</v>
       </c>
       <c r="G6">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="s">
         <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2589,10 +2589,10 @@
         <v>244.66</v>
       </c>
       <c r="F7">
-        <v>69.39999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="s">
         <v>65</v>
@@ -2618,10 +2618,10 @@
         <v>227.78</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>37.1</v>
       </c>
       <c r="G8">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="H8" t="s">
         <v>66</v>
@@ -2647,10 +2647,10 @@
         <v>227.26</v>
       </c>
       <c r="F9">
-        <v>33.2</v>
+        <v>30.2</v>
       </c>
       <c r="G9">
-        <v>15.5</v>
+        <v>19.3</v>
       </c>
       <c r="H9" t="s">
         <v>67</v>
@@ -2676,10 +2676,10 @@
         <v>205.96</v>
       </c>
       <c r="F10">
-        <v>14.2</v>
+        <v>13.5</v>
       </c>
       <c r="G10">
-        <v>30.7</v>
+        <v>28.6</v>
       </c>
       <c r="H10" t="s">
         <v>68</v>
@@ -2705,10 +2705,10 @@
         <v>214.44</v>
       </c>
       <c r="F11">
-        <v>10.9</v>
+        <v>9.1</v>
       </c>
       <c r="G11">
-        <v>38.9</v>
+        <v>38.4</v>
       </c>
       <c r="H11" t="s">
         <v>69</v>

--- a/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
+++ b/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="102">
   <si>
     <t>Michael the International Baker</t>
   </si>
@@ -55,13 +55,16 @@
     <t>The Turbanator</t>
   </si>
   <si>
-    <t>0-2-0</t>
-  </si>
-  <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
+    <t>0-3-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -124,6 +127,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -148,30 +154,30 @@
     <t>Marvin Ta</t>
   </si>
   <si>
+    <t>Chris Carbone</t>
+  </si>
+  <si>
     <t>Anthony Rizzo</t>
   </si>
   <si>
     <t>Maulin Patel</t>
   </si>
   <si>
-    <t>Chris Carbone</t>
+    <t>Victor Rojas</t>
+  </si>
+  <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
+    <t>Robbie Wilston</t>
+  </si>
+  <si>
+    <t>Kermelos Woldeyes</t>
   </si>
   <si>
     <t>Alyssa Ianovale</t>
   </si>
   <si>
-    <t>Victor Rojas</t>
-  </si>
-  <si>
-    <t>Robbie Wilston</t>
-  </si>
-  <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
-    <t>Kermelos Woldeyes</t>
-  </si>
-  <si>
     <t>Bridget Cashel</t>
   </si>
   <si>
@@ -199,61 +205,67 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>10.1-3.8-0.1</t>
   </si>
   <si>
     <t>9.6-4.3-0.1</t>
   </si>
   <si>
-    <t>8.2-5.7-0.1</t>
-  </si>
-  <si>
-    <t>8.3-5.6-0.1</t>
-  </si>
-  <si>
-    <t>7.8-6.2-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.8-0.1</t>
+    <t>9.1-4.7-0.2</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.2</t>
+  </si>
+  <si>
+    <t>7.1-6.8-0.2</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.1</t>
   </si>
   <si>
     <t>5.9-8.0-0.1</t>
   </si>
   <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>4.3-9.6-0.1</t>
+    <t>3.0-10.8-0.1</t>
+  </si>
+  <si>
+    <t>2.7-11.2-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
+    <t>9-5</t>
+  </si>
+  <si>
     <t>8-6</t>
   </si>
   <si>
-    <t>9-5</t>
-  </si>
-  <si>
     <t>7-7</t>
   </si>
   <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
-    <t>4-10</t>
+    <t>3-11</t>
+  </si>
+  <si>
+    <t>2-12</t>
   </si>
   <si>
     <t>Owners</t>
@@ -265,37 +277,37 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑10</t>
-  </si>
-  <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↓1</t>
+    <t>↑4</t>
   </si>
   <si>
     <t>↓2</t>
   </si>
   <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↓7</t>
+    <t>↓6</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -741,7 +753,7 @@
         <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -752,31 +764,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -805,13 +817,13 @@
         <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
         <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -831,7 +843,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -840,13 +852,13 @@
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" t="s">
         <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -857,16 +869,16 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -875,13 +887,13 @@
         <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
         <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -892,16 +904,16 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -910,13 +922,13 @@
         <v>11</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -927,31 +939,31 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -959,34 +971,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1032,16 +1044,16 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1050,13 +1062,13 @@
         <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1066,30 +1078,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1097,25 +1109,77 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>-2</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>-2</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1130,13 +1194,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1144,13 +1208,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1158,10 +1222,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1172,13 +1236,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1186,13 +1250,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1203,10 +1267,10 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1214,13 +1278,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1231,7 +1295,7 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1245,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1259,10 +1323,10 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1273,10 +1337,10 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1291,16 +1355,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1308,16 +1372,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1325,16 +1389,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="D3">
-        <v>-0.6000000000000001</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1342,16 +1406,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="D4">
-        <v>-0.8</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1359,16 +1423,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="D5">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1376,16 +1440,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="D6">
-        <v>0.2</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1393,16 +1457,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="D7">
-        <v>0.2</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1410,13 +1474,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D8">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -1430,13 +1494,13 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D9">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1464,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1485,306 +1549,306 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>50.6</v>
+        <v>47.6</v>
       </c>
       <c r="C2">
-        <v>21.7</v>
+        <v>25.1</v>
       </c>
       <c r="D2">
-        <v>11.1</v>
+        <v>14.1</v>
       </c>
       <c r="E2">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F2">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H2">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="I2">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>98</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>10.1</v>
+        <v>29.7</v>
       </c>
       <c r="C3">
-        <v>18.2</v>
+        <v>35.5</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>16.7</v>
+        <v>8.9</v>
       </c>
       <c r="F3">
-        <v>12.6</v>
+        <v>3.8</v>
       </c>
       <c r="G3">
-        <v>11.1</v>
+        <v>2.1</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>88.7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="C4">
-        <v>15.4</v>
+        <v>21.3</v>
       </c>
       <c r="D4">
-        <v>17.8</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>14.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G4">
-        <v>10.9</v>
+        <v>6.4</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J4">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="K4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>87.2</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>11.1</v>
+        <v>2.5</v>
       </c>
       <c r="C5">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>15.6</v>
+        <v>12.5</v>
       </c>
       <c r="E5">
-        <v>16.3</v>
+        <v>20.4</v>
       </c>
       <c r="F5">
+        <v>18.2</v>
+      </c>
+      <c r="G5">
         <v>15.3</v>
       </c>
-      <c r="G5">
-        <v>12.1</v>
-      </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>15.4</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="K5">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>85.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>10.6</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>15.2</v>
+        <v>4.7</v>
       </c>
       <c r="D6">
-        <v>15.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E6">
-        <v>13.8</v>
+        <v>15.6</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>20.1</v>
       </c>
       <c r="G6">
-        <v>11.1</v>
+        <v>21.9</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>14.8</v>
       </c>
       <c r="I6">
-        <v>5.7</v>
+        <v>10.2</v>
       </c>
       <c r="J6">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="K6">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="L6">
-        <v>81.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B7">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="C7">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="D7">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E7">
-        <v>15.3</v>
+        <v>17.6</v>
       </c>
       <c r="F7">
-        <v>14.3</v>
+        <v>18.9</v>
       </c>
       <c r="G7">
-        <v>14.8</v>
+        <v>20.1</v>
       </c>
       <c r="H7">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="I7">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="J7">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="K7">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="L7">
-        <v>69.09999999999999</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C8">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="D8">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="E8">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="F8">
-        <v>11.3</v>
+        <v>14.4</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>19.1</v>
       </c>
       <c r="H8">
-        <v>21.6</v>
+        <v>24.4</v>
       </c>
       <c r="I8">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="J8">
-        <v>14.3</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>7.7</v>
+        <v>0.1</v>
       </c>
       <c r="L8">
-        <v>37.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1792,113 +1856,113 @@
         <v>4</v>
       </c>
       <c r="B9">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="D9">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="E9">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9">
-        <v>7.3</v>
+        <v>11.1</v>
       </c>
       <c r="G9">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="H9">
-        <v>16.6</v>
+        <v>21.7</v>
       </c>
       <c r="I9">
-        <v>17.4</v>
+        <v>37</v>
       </c>
       <c r="J9">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>19.3</v>
+        <v>1.6</v>
       </c>
       <c r="L9">
-        <v>30.2</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0.1</v>
+      </c>
+      <c r="F10">
+        <v>0.4</v>
+      </c>
+      <c r="G10">
         <v>0.7</v>
       </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>4</v>
-      </c>
-      <c r="G10">
-        <v>6.2</v>
-      </c>
       <c r="H10">
-        <v>11.6</v>
+        <v>2.7</v>
       </c>
       <c r="I10">
-        <v>18.5</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>27.8</v>
+        <v>53.6</v>
       </c>
       <c r="K10">
-        <v>28.6</v>
+        <v>34.1</v>
       </c>
       <c r="L10">
-        <v>13.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>0.1</v>
       </c>
-      <c r="C11">
-        <v>0.2</v>
-      </c>
-      <c r="D11">
+      <c r="H11">
         <v>0.8</v>
       </c>
-      <c r="E11">
-        <v>1.7</v>
-      </c>
-      <c r="F11">
-        <v>1.7</v>
-      </c>
-      <c r="G11">
-        <v>4.6</v>
-      </c>
-      <c r="H11">
-        <v>8.6</v>
-      </c>
       <c r="I11">
-        <v>16.4</v>
+        <v>3.9</v>
       </c>
       <c r="J11">
-        <v>27.5</v>
+        <v>31.3</v>
       </c>
       <c r="K11">
-        <v>38.4</v>
+        <v>63.9</v>
       </c>
       <c r="L11">
-        <v>9.1</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1908,158 +1972,191 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>92.10000000000001</v>
+      </c>
+      <c r="D2">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E2">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>68.5</v>
-      </c>
-      <c r="C2">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="D2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="B3">
+        <v>79.5</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>98.8</v>
+      </c>
+      <c r="E3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C4">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D4">
+        <v>94</v>
+      </c>
+      <c r="E4">
+        <v>94.69999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C5">
+        <v>78.3</v>
+      </c>
+      <c r="D5">
+        <v>81.39999999999999</v>
+      </c>
+      <c r="E5">
+        <v>77.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2.6</v>
+      </c>
+      <c r="C6">
+        <v>28.2</v>
+      </c>
+      <c r="D6">
+        <v>65.60000000000001</v>
+      </c>
+      <c r="E6">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>36.3</v>
-      </c>
-      <c r="C3">
-        <v>92.5</v>
-      </c>
-      <c r="D3">
-        <v>89.40000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="B7">
+        <v>35.4</v>
+      </c>
+      <c r="C7">
+        <v>93.8</v>
+      </c>
+      <c r="D7">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E7">
+        <v>66.90000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>98.3</v>
-      </c>
-      <c r="C4">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="D4">
-        <v>87.40000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C5">
-        <v>80.80000000000001</v>
-      </c>
-      <c r="D5">
-        <v>83.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>97.2</v>
-      </c>
-      <c r="C6">
-        <v>85.2</v>
-      </c>
-      <c r="D6">
-        <v>83.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>98.2</v>
-      </c>
-      <c r="C7">
-        <v>70</v>
-      </c>
-      <c r="D7">
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B8">
-        <v>7.9</v>
+        <v>99.5</v>
       </c>
       <c r="C8">
-        <v>38.3</v>
+        <v>92.30000000000001</v>
       </c>
       <c r="D8">
-        <v>34.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>53.8</v>
+      </c>
+      <c r="E8">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>30.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>35.2</v>
+      </c>
+      <c r="E9">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>3.2</v>
+      </c>
+      <c r="D10">
+        <v>0.8</v>
+      </c>
+      <c r="E10">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>56.59999999999999</v>
-      </c>
-      <c r="C10">
-        <v>11.9</v>
-      </c>
-      <c r="D10">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B11">
-        <v>37</v>
+        <v>51.8</v>
       </c>
       <c r="C11">
-        <v>9.300000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="D11">
-        <v>7.9</v>
+        <v>0.2</v>
+      </c>
+      <c r="E11">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -2074,28 +2171,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2106,25 +2203,25 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>102.98</v>
+        <v>95.53</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>124.15</v>
+        <v>124.57</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H2">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2132,28 +2229,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>107.22</v>
+        <v>117.04</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>122.38</v>
+        <v>121.34</v>
       </c>
       <c r="G3">
-        <v>0.542</v>
+        <v>0.424</v>
       </c>
       <c r="H3">
         <v>1.2</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2161,28 +2258,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>122.45</v>
+        <v>105.17</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>121.46</v>
+        <v>121.3</v>
       </c>
       <c r="G4">
-        <v>0.417</v>
+        <v>0.545</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2190,28 +2287,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>123.55</v>
+        <v>125.91</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>121.15</v>
+        <v>121.58</v>
       </c>
       <c r="G5">
-        <v>0.375</v>
+        <v>0.455</v>
       </c>
       <c r="H5">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2219,28 +2316,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>113.89</v>
+        <v>124.3</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>122.78</v>
+        <v>120.37</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H6">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2248,28 +2345,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>127.74</v>
+        <v>122.61</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>120.05</v>
+        <v>122.64</v>
       </c>
       <c r="G7">
-        <v>0.542</v>
+        <v>0.485</v>
       </c>
       <c r="H7">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2280,25 +2377,25 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>128.97</v>
+        <v>140.84</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>119.39</v>
+        <v>119.48</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H8">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2306,28 +2403,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>122.33</v>
+        <v>115.93</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9">
-        <v>120.58</v>
+        <v>120.15</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H9">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2335,28 +2432,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>113.63</v>
+        <v>119.16</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>120.77</v>
+        <v>118.84</v>
       </c>
       <c r="G10">
-        <v>0.583</v>
+        <v>0.455</v>
       </c>
       <c r="H10">
         <v>-1.6</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2367,25 +2464,25 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>146.89</v>
+        <v>140.05</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11">
-        <v>116.93</v>
+        <v>116.28</v>
       </c>
       <c r="G11">
-        <v>0.542</v>
+        <v>0.515</v>
       </c>
       <c r="H11">
-        <v>-2.1</v>
+        <v>-3.3</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2400,234 +2497,234 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2">
-        <v>146.89</v>
+        <v>140.84</v>
       </c>
       <c r="E2">
-        <v>293.78</v>
+        <v>422.52</v>
       </c>
       <c r="F2">
-        <v>98</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D3">
-        <v>127.74</v>
+        <v>140.0466666666667</v>
       </c>
       <c r="E3">
-        <v>255.48</v>
+        <v>420.14</v>
       </c>
       <c r="F3">
-        <v>88.7</v>
+        <v>98</v>
       </c>
       <c r="G3">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>123.55</v>
+        <v>125.9133333333333</v>
       </c>
       <c r="E4">
-        <v>247.1</v>
+        <v>377.74</v>
       </c>
       <c r="F4">
-        <v>87.2</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="G4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>122.45</v>
+        <v>122.6133333333333</v>
       </c>
       <c r="E5">
-        <v>244.9</v>
+        <v>367.84</v>
       </c>
       <c r="F5">
-        <v>85.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G5">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>128.97</v>
+        <v>119.16</v>
       </c>
       <c r="E6">
-        <v>257.94</v>
+        <v>357.48</v>
       </c>
       <c r="F6">
-        <v>81.2</v>
+        <v>74</v>
       </c>
       <c r="G6">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>122.33</v>
+        <v>124.3</v>
       </c>
       <c r="E7">
-        <v>244.66</v>
+        <v>372.9</v>
       </c>
       <c r="F7">
-        <v>69.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="G7">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8">
-        <v>113.89</v>
+        <v>117.04</v>
       </c>
       <c r="E8">
-        <v>227.78</v>
+        <v>351.12</v>
       </c>
       <c r="F8">
-        <v>37.1</v>
+        <v>54</v>
       </c>
       <c r="G8">
-        <v>7.7</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2635,86 +2732,86 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>113.63</v>
+        <v>115.9333333333333</v>
       </c>
       <c r="E9">
-        <v>227.26</v>
+        <v>347.8</v>
       </c>
       <c r="F9">
-        <v>30.2</v>
+        <v>31.7</v>
       </c>
       <c r="G9">
-        <v>19.3</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>102.98</v>
+        <v>105.1666666666667</v>
       </c>
       <c r="E10">
-        <v>205.96</v>
+        <v>315.5</v>
       </c>
       <c r="F10">
-        <v>13.5</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>28.6</v>
+        <v>34.1</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>107.22</v>
+        <v>95.53333333333332</v>
       </c>
       <c r="E11">
-        <v>214.44</v>
+        <v>286.6</v>
       </c>
       <c r="F11">
-        <v>9.1</v>
+        <v>0.1</v>
       </c>
       <c r="G11">
-        <v>38.4</v>
+        <v>63.9</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2729,19 +2826,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2752,16 +2849,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2772,16 +2869,16 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2789,19 +2886,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2809,19 +2906,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2829,19 +2926,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2852,16 +2949,16 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2869,19 +2966,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2892,16 +2989,16 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2912,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>-8</v>
@@ -2921,7 +3018,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2932,16 +3029,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11">
-        <v>-11</v>
+        <v>-17</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2951,21 +3048,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>94</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -2975,11 +3075,14 @@
       <c r="C2">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2989,53 +3092,65 @@
       <c r="C3">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>-4</v>
+      </c>
+      <c r="C4">
+        <v>-2</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B6">
         <v>6</v>
       </c>
-      <c r="C4">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -3045,25 +3160,31 @@
       <c r="C7">
         <v>-2</v>
       </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
         <v>-2</v>
       </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -3073,11 +3194,14 @@
       <c r="C9">
         <v>-6</v>
       </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="D9">
+        <v>-2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -3087,11 +3211,14 @@
       <c r="C10">
         <v>-8</v>
       </c>
-      <c r="D10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10">
+        <v>-8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3101,8 +3228,11 @@
       <c r="C11">
         <v>-11</v>
       </c>
-      <c r="D11" t="s">
-        <v>88</v>
+      <c r="D11">
+        <v>-17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
+++ b/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="102">
-  <si>
-    <t>Michael the International Baker</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="105">
+  <si>
+    <t>LaPortAuthority</t>
   </si>
   <si>
     <t>Maulin's Monstrous Team</t>
@@ -55,16 +55,19 @@
     <t>The Turbanator</t>
   </si>
   <si>
-    <t>0-3-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -154,30 +160,30 @@
     <t>Marvin Ta</t>
   </si>
   <si>
+    <t>Maulin Patel</t>
+  </si>
+  <si>
+    <t>Victor Rojas</t>
+  </si>
+  <si>
     <t>Chris Carbone</t>
   </si>
   <si>
+    <t>Robbie Wilston</t>
+  </si>
+  <si>
     <t>Anthony Rizzo</t>
   </si>
   <si>
-    <t>Maulin Patel</t>
-  </si>
-  <si>
-    <t>Victor Rojas</t>
-  </si>
-  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Robbie Wilston</t>
+    <t>Alyssa Ianovale</t>
   </si>
   <si>
     <t>Kermelos Woldeyes</t>
   </si>
   <si>
-    <t>Alyssa Ianovale</t>
-  </si>
-  <si>
     <t>Bridget Cashel</t>
   </si>
   <si>
@@ -205,51 +211,48 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>10.1-3.8-0.1</t>
-  </si>
-  <si>
-    <t>9.6-4.3-0.1</t>
-  </si>
-  <si>
-    <t>9.1-4.7-0.2</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.2</t>
-  </si>
-  <si>
-    <t>7.1-6.8-0.2</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>3.0-10.8-0.1</t>
-  </si>
-  <si>
-    <t>2.7-11.2-0.1</t>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>10.3-3.6-0.1</t>
+  </si>
+  <si>
+    <t>8.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>8.2-5.6-0.1</t>
+  </si>
+  <si>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.2-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>5.1-8.8-0.1</t>
+  </si>
+  <si>
+    <t>4.4-9.5-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>10-4</t>
-  </si>
-  <si>
     <t>9-5</t>
   </si>
   <si>
@@ -262,10 +265,10 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>3-11</t>
-  </si>
-  <si>
-    <t>2-12</t>
+    <t>5-9</t>
+  </si>
+  <si>
+    <t>4-10</t>
   </si>
   <si>
     <t>Owners</t>
@@ -277,28 +280,31 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↑1</t>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓1</t>
   </si>
   <si>
     <t>↓4</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓6</t>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↓8</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -308,6 +314,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -744,7 +753,7 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -764,31 +773,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
       <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -799,31 +808,31 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -843,19 +852,19 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" t="s">
         <v>12</v>
@@ -866,34 +875,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -904,31 +913,31 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -948,19 +957,19 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
@@ -983,22 +992,22 @@
         <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" t="s">
         <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1044,31 +1053,31 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
         <v>12</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1078,30 +1087,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1109,25 +1118,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
       <c r="E2">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="F2">
+        <v>11</v>
+      </c>
+      <c r="G2">
         <v>18</v>
       </c>
-      <c r="G2">
-        <v>14</v>
-      </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1135,22 +1144,22 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>
@@ -1161,24 +1170,76 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>-2</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="H4" t="s">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>-2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1194,13 +1255,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1208,13 +1269,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1222,10 +1283,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1236,13 +1297,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1253,7 +1314,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1264,13 +1325,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1278,13 +1339,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1292,13 +1353,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1306,10 +1367,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
@@ -1320,10 +1381,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1334,13 +1395,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1355,16 +1416,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1375,10 +1436,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="D2">
-        <v>0.2000000000000002</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1389,16 +1450,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="D3">
-        <v>-0.8999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1406,16 +1467,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="D4">
-        <v>1.1</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1423,16 +1484,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D5">
-        <v>-0.2</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1440,16 +1501,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D6">
-        <v>-0.3999999999999999</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1457,16 +1518,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D7">
-        <v>-0.3999999999999999</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1474,13 +1535,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -1491,13 +1552,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -1508,16 +1569,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="D10">
-        <v>-0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1525,13 +1586,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="D11">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1549,40 +1610,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1590,31 +1651,31 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>47.6</v>
+        <v>66.2</v>
       </c>
       <c r="C2">
-        <v>25.1</v>
+        <v>18.7</v>
       </c>
       <c r="D2">
-        <v>14.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E2">
-        <v>8.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="G2">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
         <v>0.2</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1628,37 +1689,37 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>29.7</v>
+        <v>18.1</v>
       </c>
       <c r="C3">
-        <v>35.5</v>
+        <v>33.1</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>20.7</v>
       </c>
       <c r="E3">
-        <v>8.9</v>
+        <v>12.8</v>
       </c>
       <c r="F3">
-        <v>3.8</v>
+        <v>8.1</v>
       </c>
       <c r="G3">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L3">
-        <v>98</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1666,75 +1727,75 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>15.7</v>
+        <v>7.6</v>
       </c>
       <c r="C4">
-        <v>21.3</v>
+        <v>15.9</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>22.6</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>19.4</v>
       </c>
       <c r="F4">
-        <v>9.800000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="G4">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H4">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="I4">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J4">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L4">
-        <v>95.2</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>17.9</v>
       </c>
       <c r="D5">
-        <v>12.5</v>
+        <v>22.5</v>
       </c>
       <c r="E5">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="F5">
-        <v>18.2</v>
+        <v>14.6</v>
       </c>
       <c r="G5">
-        <v>15.3</v>
+        <v>10.5</v>
       </c>
       <c r="H5">
-        <v>15.4</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>1.8</v>
       </c>
       <c r="J5">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>74.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1742,75 +1803,75 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="C6">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D6">
-        <v>9.699999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="E6">
-        <v>15.6</v>
+        <v>18.8</v>
       </c>
       <c r="F6">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="G6">
-        <v>21.9</v>
+        <v>17.2</v>
       </c>
       <c r="H6">
-        <v>14.8</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="J6">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="K6">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="L6">
-        <v>74</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="C7">
         <v>3.3</v>
       </c>
       <c r="D7">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="E7">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="F7">
-        <v>18.9</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>20.1</v>
+        <v>22.3</v>
       </c>
       <c r="H7">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="I7">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="J7">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="K7">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="L7">
-        <v>71.3</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1818,42 +1879,42 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="C8">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="D8">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="E8">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="F8">
-        <v>14.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G8">
+        <v>13.4</v>
+      </c>
+      <c r="H8">
+        <v>18.4</v>
+      </c>
+      <c r="I8">
+        <v>19.9</v>
+      </c>
+      <c r="J8">
         <v>19.1</v>
       </c>
-      <c r="H8">
-        <v>24.4</v>
-      </c>
-      <c r="I8">
-        <v>18.5</v>
-      </c>
-      <c r="J8">
-        <v>3</v>
-      </c>
       <c r="K8">
-        <v>0.1</v>
+        <v>12.8</v>
       </c>
       <c r="L8">
-        <v>54</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>0.1</v>
@@ -1862,31 +1923,31 @@
         <v>0.8</v>
       </c>
       <c r="D9">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="E9">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>11.1</v>
+        <v>6.4</v>
       </c>
       <c r="G9">
-        <v>13.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H9">
-        <v>21.7</v>
+        <v>14.3</v>
       </c>
       <c r="I9">
-        <v>37</v>
+        <v>19.1</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>24.8</v>
       </c>
       <c r="K9">
-        <v>1.6</v>
+        <v>22.8</v>
       </c>
       <c r="L9">
-        <v>31.7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1897,72 +1958,72 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
+        <v>3.1</v>
       </c>
       <c r="F10">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="G10">
-        <v>0.7</v>
+        <v>8.4</v>
       </c>
       <c r="H10">
-        <v>2.7</v>
+        <v>19.1</v>
       </c>
       <c r="I10">
-        <v>8.4</v>
+        <v>21.3</v>
       </c>
       <c r="J10">
-        <v>53.6</v>
+        <v>20.6</v>
       </c>
       <c r="K10">
-        <v>34.1</v>
+        <v>21</v>
       </c>
       <c r="L10">
-        <v>1.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>5.3</v>
       </c>
       <c r="H11">
-        <v>0.8</v>
+        <v>9.6</v>
       </c>
       <c r="I11">
-        <v>3.9</v>
+        <v>17.4</v>
       </c>
       <c r="J11">
-        <v>31.3</v>
+        <v>24.6</v>
       </c>
       <c r="K11">
-        <v>63.9</v>
+        <v>38.8</v>
       </c>
       <c r="L11">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -1972,24 +2033,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1997,16 +2061,19 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>92.10000000000001</v>
+        <v>91.60000000000001</v>
       </c>
       <c r="D2">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E2">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F2">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -2014,50 +2081,59 @@
         <v>79.5</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D3">
-        <v>98.8</v>
+        <v>98.5</v>
       </c>
       <c r="E3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="F3">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>34.3</v>
+      </c>
+      <c r="C4">
+        <v>94</v>
+      </c>
+      <c r="D4">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="E4">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="F4">
+        <v>90.40000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="C4">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="D4">
-        <v>94</v>
-      </c>
-      <c r="E4">
-        <v>94.69999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B5">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C5">
-        <v>78.3</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="D5">
-        <v>81.39999999999999</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="E5">
-        <v>77.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>87</v>
+      </c>
+      <c r="F5">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -2065,33 +2141,39 @@
         <v>2.6</v>
       </c>
       <c r="C6">
-        <v>28.2</v>
+        <v>28.6</v>
       </c>
       <c r="D6">
-        <v>65.60000000000001</v>
+        <v>69</v>
       </c>
       <c r="E6">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F6">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B7">
-        <v>35.4</v>
+        <v>99.7</v>
       </c>
       <c r="C7">
-        <v>93.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D7">
-        <v>70.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E7">
-        <v>66.90000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>61.7</v>
+      </c>
+      <c r="F7">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -2099,64 +2181,76 @@
         <v>99.5</v>
       </c>
       <c r="C8">
-        <v>92.30000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="D8">
-        <v>53.8</v>
+        <v>55.40000000000001</v>
       </c>
       <c r="E8">
-        <v>55.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>24.3</v>
+      </c>
+      <c r="F8">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9">
+        <v>54.50000000000001</v>
+      </c>
+      <c r="C9">
+        <v>5.1</v>
+      </c>
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="C9">
-        <v>17</v>
-      </c>
-      <c r="D9">
-        <v>35.2</v>
-      </c>
       <c r="E9">
-        <v>32.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>19.5</v>
+      </c>
+      <c r="F9">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B10">
-        <v>32</v>
+        <v>30.5</v>
       </c>
       <c r="C10">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="D10">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="E10">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>25.5</v>
+      </c>
+      <c r="F10">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11">
-        <v>51.8</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>3.7</v>
+        <v>15.6</v>
       </c>
       <c r="D11">
-        <v>0.2</v>
+        <v>33.2</v>
       </c>
       <c r="E11">
-        <v>0.4</v>
+        <v>11.2</v>
+      </c>
+      <c r="F11">
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2171,28 +2265,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2203,25 +2297,25 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>95.53</v>
+        <v>109.72</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>124.57</v>
+        <v>123.84</v>
       </c>
       <c r="G2">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2229,28 +2323,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>117.04</v>
+        <v>122.05</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>121.34</v>
+        <v>120.35</v>
       </c>
       <c r="G3">
-        <v>0.424</v>
+        <v>0.45</v>
       </c>
       <c r="H3">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2258,28 +2352,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>105.17</v>
+        <v>127.51</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>121.3</v>
+        <v>121.18</v>
       </c>
       <c r="G4">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2287,28 +2381,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>125.91</v>
+        <v>112.44</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>121.58</v>
+        <v>121.73</v>
       </c>
       <c r="G5">
-        <v>0.455</v>
+        <v>0.475</v>
       </c>
       <c r="H5">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2316,28 +2410,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>124.3</v>
+        <v>138.63</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>120.37</v>
+        <v>119.7</v>
       </c>
       <c r="G6">
-        <v>0.545</v>
+        <v>0.475</v>
       </c>
       <c r="H6">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2345,28 +2439,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>122.61</v>
+        <v>114.92</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>122.64</v>
+        <v>121.23</v>
       </c>
       <c r="G7">
-        <v>0.485</v>
+        <v>0.525</v>
       </c>
       <c r="H7">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2374,28 +2468,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>140.84</v>
+        <v>120.91</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>119.48</v>
+        <v>123.25</v>
       </c>
       <c r="G8">
-        <v>0.545</v>
+        <v>0.525</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2403,28 +2497,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>115.93</v>
+        <v>124.54</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9">
-        <v>120.15</v>
+        <v>121.77</v>
       </c>
       <c r="G9">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2432,28 +2526,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>119.16</v>
+        <v>110.78</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>118.84</v>
+        <v>122.61</v>
       </c>
       <c r="G10">
-        <v>0.455</v>
+        <v>0.55</v>
       </c>
       <c r="H10">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2464,25 +2558,25 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>140.05</v>
+        <v>133.29</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11">
-        <v>116.28</v>
+        <v>119.12</v>
       </c>
       <c r="G11">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-3.3</v>
+        <v>-2</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2497,31 +2591,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2529,16 +2623,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D2">
-        <v>140.84</v>
+        <v>138.635</v>
       </c>
       <c r="E2">
-        <v>422.52</v>
+        <v>554.54</v>
       </c>
       <c r="F2">
         <v>99.59999999999999</v>
@@ -2547,10 +2641,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2558,28 +2652,28 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D3">
-        <v>140.0466666666667</v>
+        <v>133.29</v>
       </c>
       <c r="E3">
-        <v>420.14</v>
+        <v>533.16</v>
       </c>
       <c r="F3">
-        <v>98</v>
+        <v>97.2</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2590,54 +2684,54 @@
         <v>62</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>125.9133333333333</v>
+        <v>122.05</v>
       </c>
       <c r="E4">
-        <v>377.74</v>
+        <v>488.2</v>
       </c>
       <c r="F4">
-        <v>95.19999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>122.6133333333333</v>
+        <v>127.505</v>
       </c>
       <c r="E5">
-        <v>367.84</v>
+        <v>510.02</v>
       </c>
       <c r="F5">
-        <v>74.90000000000001</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2645,57 +2739,57 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>119.16</v>
+        <v>124.54</v>
       </c>
       <c r="E6">
-        <v>357.48</v>
+        <v>498.16</v>
       </c>
       <c r="F6">
-        <v>74</v>
+        <v>79.60000000000001</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>124.3</v>
+        <v>120.905</v>
       </c>
       <c r="E7">
-        <v>372.9</v>
+        <v>483.62</v>
       </c>
       <c r="F7">
-        <v>71.3</v>
+        <v>65.10000000000001</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2703,57 +2797,57 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C8">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>117.04</v>
+        <v>112.44</v>
       </c>
       <c r="E8">
-        <v>351.12</v>
+        <v>449.76</v>
       </c>
       <c r="F8">
-        <v>54</v>
+        <v>29.8</v>
       </c>
       <c r="G8">
-        <v>0.1</v>
+        <v>12.8</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>115.9333333333333</v>
+        <v>109.72</v>
       </c>
       <c r="E9">
-        <v>347.8</v>
+        <v>438.88</v>
       </c>
       <c r="F9">
-        <v>31.7</v>
+        <v>19</v>
       </c>
       <c r="G9">
-        <v>1.6</v>
+        <v>22.8</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2761,57 +2855,57 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>105.1666666666667</v>
+        <v>114.92</v>
       </c>
       <c r="E10">
-        <v>315.5</v>
+        <v>459.68</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>18</v>
       </c>
       <c r="G10">
-        <v>34.1</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D11">
-        <v>95.53333333333332</v>
+        <v>110.775</v>
       </c>
       <c r="E11">
-        <v>286.6</v>
+        <v>443.1</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>9.6</v>
       </c>
       <c r="G11">
-        <v>63.9</v>
+        <v>38.8</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2826,19 +2920,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2849,16 +2943,16 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2866,19 +2960,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2886,19 +2980,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2906,19 +3000,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2929,16 +3023,16 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2952,13 +3046,13 @@
         <v>48</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2966,19 +3060,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2986,19 +3080,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3009,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>-8</v>
@@ -3018,7 +3112,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3026,19 +3120,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D11">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3048,24 +3142,27 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3078,62 +3175,74 @@
       <c r="D2">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>-4</v>
+      </c>
+      <c r="C3">
+        <v>-2</v>
+      </c>
+      <c r="D3">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <v>-1</v>
       </c>
-      <c r="C3">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D3">
+      <c r="D5">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>-4</v>
-      </c>
-      <c r="C4">
-        <v>-2</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -3146,11 +3255,14 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -3163,45 +3275,54 @@
       <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="D8">
         <v>-2</v>
       </c>
-      <c r="E8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8">
+        <v>-6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="C9">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="D9">
-        <v>-2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>-17</v>
+      </c>
+      <c r="E9">
+        <v>-7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -3214,25 +3335,31 @@
       <c r="D10">
         <v>-8</v>
       </c>
-      <c r="E10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10">
+        <v>-8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B11">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>-17</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
+        <v>-2</v>
+      </c>
+      <c r="E11">
+        <v>-10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
+++ b/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="106">
   <si>
     <t>LaPortAuthority</t>
   </si>
@@ -55,19 +55,22 @@
     <t>The Turbanator</t>
   </si>
   <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +139,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -160,33 +166,33 @@
     <t>Marvin Ta</t>
   </si>
   <si>
+    <t>Chris Carbone</t>
+  </si>
+  <si>
+    <t>Anthony Rizzo</t>
+  </si>
+  <si>
     <t>Maulin Patel</t>
   </si>
   <si>
+    <t>Kermelos Woldeyes</t>
+  </si>
+  <si>
     <t>Victor Rojas</t>
   </si>
   <si>
-    <t>Chris Carbone</t>
-  </si>
-  <si>
     <t>Robbie Wilston</t>
   </si>
   <si>
-    <t>Anthony Rizzo</t>
-  </si>
-  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
+    <t>Bridget Cashel</t>
+  </si>
+  <si>
     <t>Alyssa Ianovale</t>
   </si>
   <si>
-    <t>Kermelos Woldeyes</t>
-  </si>
-  <si>
-    <t>Bridget Cashel</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -211,49 +217,49 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>10.3-3.6-0.1</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
-  </si>
-  <si>
-    <t>8.2-5.6-0.1</t>
-  </si>
-  <si>
-    <t>8.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.2-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.2-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>5.1-8.8-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>10.7-3.2-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.5-0.1</t>
+  </si>
+  <si>
+    <t>8.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>4.1-9.8-0.1</t>
+  </si>
+  <si>
+    <t>4.0-9.9-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>9-5</t>
+    <t>10-4</t>
   </si>
   <si>
     <t>8-6</t>
@@ -265,9 +271,6 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
@@ -280,31 +283,28 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↑7</t>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓1</t>
   </si>
   <si>
     <t>↑3</t>
   </si>
   <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↑10</t>
-  </si>
-  <si>
-    <t>↓8</t>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓9</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -738,22 +741,22 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -762,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -773,13 +776,13 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -788,16 +791,16 @@
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -805,34 +808,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" t="s">
         <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -840,34 +843,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
       <c r="J5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" t="s">
         <v>11</v>
-      </c>
-      <c r="K5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -875,34 +878,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -910,19 +913,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -934,10 +937,10 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -948,10 +951,10 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -966,13 +969,13 @@
         <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
         <v>11</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -980,28 +983,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" t="s">
         <v>11</v>
@@ -1015,34 +1018,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1050,19 +1053,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1071,13 +1074,13 @@
         <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
         <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1087,30 +1090,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1222,24 +1225,50 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>-5</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>3</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>-2</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1255,13 +1284,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1272,10 +1301,10 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1283,13 +1312,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1300,7 +1329,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1311,13 +1340,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1325,13 +1354,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1339,13 +1368,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1353,13 +1382,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1370,10 +1399,10 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1381,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1395,13 +1424,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1416,16 +1445,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1436,13 +1465,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="D2">
         <v>-0.2000000000000002</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1450,13 +1479,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1470,13 +1499,13 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="D4">
-        <v>-0.7000000000000002</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1484,13 +1513,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D5">
-        <v>0.2999999999999998</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1501,16 +1530,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="D6">
-        <v>0.2000000000000002</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1518,16 +1547,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="D7">
-        <v>0.2000000000000002</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1538,13 +1567,13 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="D8">
-        <v>-0.3</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1552,16 +1581,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>-0.6000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1569,16 +1598,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1586,13 +1615,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1610,40 +1639,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1651,379 +1680,379 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>66.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C2">
-        <v>18.7</v>
+        <v>16.5</v>
       </c>
       <c r="D2">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="F2">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>18.1</v>
+        <v>13.3</v>
       </c>
       <c r="C3">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="D3">
-        <v>20.7</v>
+        <v>25.2</v>
       </c>
       <c r="E3">
-        <v>12.8</v>
+        <v>13.9</v>
       </c>
       <c r="F3">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="G3">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1.2</v>
       </c>
       <c r="I3">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>97.2</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="C4">
-        <v>15.9</v>
+        <v>25.3</v>
       </c>
       <c r="D4">
-        <v>22.6</v>
+        <v>25.4</v>
       </c>
       <c r="E4">
-        <v>19.4</v>
+        <v>20.9</v>
       </c>
       <c r="F4">
-        <v>16.8</v>
+        <v>11.9</v>
       </c>
       <c r="G4">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="H4">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="I4">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J4">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>91.5</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="C5">
-        <v>17.9</v>
+        <v>16.8</v>
       </c>
       <c r="D5">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>20.3</v>
+        <v>22.2</v>
       </c>
       <c r="F5">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="G5">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="I5">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J5">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>90.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="C6">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="D6">
-        <v>13.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E6">
-        <v>18.8</v>
+        <v>16.9</v>
       </c>
       <c r="F6">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="G6">
-        <v>17.2</v>
+        <v>21.1</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>15.2</v>
       </c>
       <c r="I6">
-        <v>6.1</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="K6">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="L6">
-        <v>79.59999999999999</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="D7">
-        <v>8.1</v>
+        <v>5.2</v>
       </c>
       <c r="E7">
-        <v>13.8</v>
+        <v>10.4</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="G7">
-        <v>22.3</v>
+        <v>19.2</v>
       </c>
       <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
         <v>15.6</v>
       </c>
-      <c r="I7">
-        <v>10.9</v>
-      </c>
       <c r="J7">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="K7">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="L7">
-        <v>65.09999999999999</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C8">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
         <v>2.2</v>
       </c>
       <c r="E8">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="F8">
-        <v>8.199999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="G8">
-        <v>13.4</v>
+        <v>18.7</v>
       </c>
       <c r="H8">
-        <v>18.4</v>
+        <v>22.6</v>
       </c>
       <c r="I8">
-        <v>19.9</v>
+        <v>21.8</v>
       </c>
       <c r="J8">
-        <v>19.1</v>
+        <v>11.3</v>
       </c>
       <c r="K8">
-        <v>12.8</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>29.8</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9">
         <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D9">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="F9">
-        <v>6.4</v>
+        <v>12.9</v>
       </c>
       <c r="G9">
-        <v>8.800000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="H9">
-        <v>14.3</v>
+        <v>19.7</v>
       </c>
       <c r="I9">
-        <v>19.1</v>
+        <v>22.4</v>
       </c>
       <c r="J9">
-        <v>24.8</v>
+        <v>12.6</v>
       </c>
       <c r="K9">
-        <v>22.8</v>
+        <v>5.7</v>
       </c>
       <c r="L9">
-        <v>19</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0.2</v>
+      </c>
+      <c r="E10">
         <v>0.4</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>3.1</v>
-      </c>
       <c r="F10">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="G10">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="H10">
-        <v>19.1</v>
+        <v>5.7</v>
       </c>
       <c r="I10">
-        <v>21.3</v>
+        <v>16.4</v>
       </c>
       <c r="J10">
-        <v>20.6</v>
+        <v>36.9</v>
       </c>
       <c r="K10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="L10">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.1</v>
       </c>
-      <c r="C11">
-        <v>0.2</v>
-      </c>
       <c r="D11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="H11">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="I11">
-        <v>17.4</v>
+        <v>11.1</v>
       </c>
       <c r="J11">
-        <v>24.6</v>
+        <v>28.8</v>
       </c>
       <c r="K11">
-        <v>38.8</v>
+        <v>51.7</v>
       </c>
       <c r="L11">
-        <v>9.6</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -2033,27 +2062,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2061,196 +2093,226 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>91.60000000000001</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="D2">
-        <v>99.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="E2">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F2">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C3">
+        <v>91.2</v>
+      </c>
+      <c r="D3">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="E3">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="F3">
+        <v>97.8</v>
+      </c>
+      <c r="G3">
+        <v>97.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>3.2</v>
+      </c>
+      <c r="C4">
+        <v>26.4</v>
+      </c>
+      <c r="D4">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="E4">
+        <v>86.2</v>
+      </c>
+      <c r="F4">
+        <v>95.5</v>
+      </c>
+      <c r="G4">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>79.5</v>
-      </c>
-      <c r="C3">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D3">
-        <v>98.5</v>
-      </c>
-      <c r="E3">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="F3">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>34.3</v>
-      </c>
-      <c r="C4">
-        <v>94</v>
-      </c>
-      <c r="D4">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="E4">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="F4">
-        <v>90.40000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B5">
-        <v>99.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C5">
-        <v>89.60000000000001</v>
+        <v>100</v>
       </c>
       <c r="D5">
+        <v>98.8</v>
+      </c>
+      <c r="E5">
+        <v>98</v>
+      </c>
+      <c r="F5">
         <v>95.19999999999999</v>
       </c>
-      <c r="E5">
-        <v>87</v>
-      </c>
-      <c r="F5">
-        <v>90.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>93.40000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>2.6</v>
+        <v>99.5</v>
       </c>
       <c r="C6">
-        <v>28.6</v>
+        <v>79</v>
       </c>
       <c r="D6">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E6">
-        <v>85.90000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="F6">
-        <v>83.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>68.30000000000001</v>
+      </c>
+      <c r="G6">
+        <v>72.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>99.7</v>
+        <v>29.4</v>
       </c>
       <c r="C7">
-        <v>80.40000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="D7">
-        <v>78.40000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="E7">
-        <v>61.7</v>
+        <v>23.1</v>
       </c>
       <c r="F7">
-        <v>61.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>57.49999999999999</v>
+      </c>
+      <c r="G7">
+        <v>58.59999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B8">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C8">
-        <v>91.3</v>
+        <v>90.7</v>
       </c>
       <c r="D8">
-        <v>55.40000000000001</v>
+        <v>55.60000000000001</v>
       </c>
       <c r="E8">
-        <v>24.3</v>
+        <v>23.3</v>
       </c>
       <c r="F8">
-        <v>27.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>42.1</v>
+      </c>
+      <c r="G8">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>36.2</v>
+      </c>
+      <c r="C9">
+        <v>93.89999999999999</v>
+      </c>
+      <c r="D9">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E9">
+        <v>89.7</v>
+      </c>
+      <c r="F9">
+        <v>35.9</v>
+      </c>
+      <c r="G9">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>15.6</v>
+      </c>
+      <c r="D10">
+        <v>34.1</v>
+      </c>
+      <c r="E10">
+        <v>9.6</v>
+      </c>
+      <c r="F10">
+        <v>4.9</v>
+      </c>
+      <c r="G10">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>54.50000000000001</v>
-      </c>
-      <c r="C9">
-        <v>5.1</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>19.5</v>
-      </c>
-      <c r="F9">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>30.5</v>
-      </c>
-      <c r="C10">
-        <v>3.9</v>
-      </c>
-      <c r="D10">
+      <c r="B11">
+        <v>52.1</v>
+      </c>
+      <c r="C11">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="D11">
         <v>0.3</v>
       </c>
-      <c r="E10">
-        <v>25.5</v>
-      </c>
-      <c r="F10">
-        <v>20.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>15.6</v>
-      </c>
-      <c r="D11">
-        <v>33.2</v>
-      </c>
       <c r="E11">
-        <v>11.2</v>
+        <v>20.3</v>
       </c>
       <c r="F11">
-        <v>9.199999999999999</v>
+        <v>2.8</v>
+      </c>
+      <c r="G11">
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>
@@ -2265,28 +2327,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2297,25 +2359,25 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>109.72</v>
+        <v>98.34</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>123.84</v>
+        <v>126.14</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2323,28 +2385,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>122.05</v>
+        <v>119.2</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>120.35</v>
+        <v>123.82</v>
       </c>
       <c r="G3">
-        <v>0.45</v>
+        <v>0.511</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2352,28 +2414,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>127.51</v>
+        <v>122.72</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>121.18</v>
+        <v>123.43</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H4">
         <v>0.6</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2381,28 +2443,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>112.44</v>
+        <v>129.89</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>121.73</v>
+        <v>122.63</v>
       </c>
       <c r="G5">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2410,28 +2472,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>138.63</v>
+        <v>111.85</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>119.7</v>
+        <v>124.64</v>
       </c>
       <c r="G6">
-        <v>0.475</v>
+        <v>0.533</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2439,28 +2501,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>114.92</v>
+        <v>118.92</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>121.23</v>
+        <v>123.85</v>
       </c>
       <c r="G7">
-        <v>0.525</v>
+        <v>0.511</v>
       </c>
       <c r="H7">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2468,28 +2530,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8">
+        <v>144.51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>121.01</v>
+      </c>
+      <c r="G8">
+        <v>0.467</v>
+      </c>
+      <c r="H8">
+        <v>-0.6</v>
+      </c>
+      <c r="I8">
         <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8">
-        <v>120.91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>123.25</v>
-      </c>
-      <c r="G8">
-        <v>0.525</v>
-      </c>
-      <c r="H8">
-        <v>-0.2</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2497,28 +2559,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>124.54</v>
+        <v>125.91</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>121.77</v>
+        <v>123.08</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H9">
         <v>-0.6</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2526,28 +2588,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>110.78</v>
+        <v>130.17</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>122.61</v>
+        <v>122.6</v>
       </c>
       <c r="G10">
-        <v>0.55</v>
+        <v>0.489</v>
       </c>
       <c r="H10">
         <v>-0.8</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2555,28 +2617,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>133.29</v>
+        <v>132.08</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11">
-        <v>119.12</v>
+        <v>122.39</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H11">
-        <v>-2</v>
+        <v>-1.3</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2591,31 +2653,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2623,289 +2685,289 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>138.635</v>
+        <v>144.508</v>
       </c>
       <c r="E2">
-        <v>554.54</v>
+        <v>722.54</v>
       </c>
       <c r="F2">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>133.29</v>
+        <v>129.888</v>
       </c>
       <c r="E3">
-        <v>533.16</v>
+        <v>649.4400000000001</v>
       </c>
       <c r="F3">
-        <v>97.2</v>
+        <v>98.5</v>
       </c>
       <c r="G3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>122.05</v>
+        <v>132.076</v>
       </c>
       <c r="E4">
-        <v>488.2</v>
+        <v>660.38</v>
       </c>
       <c r="F4">
-        <v>91.5</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="G4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>127.505</v>
+        <v>130.172</v>
       </c>
       <c r="E5">
-        <v>510.02</v>
+        <v>650.86</v>
       </c>
       <c r="F5">
-        <v>90.60000000000001</v>
+        <v>92.10000000000001</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D6">
-        <v>124.54</v>
+        <v>125.912</v>
       </c>
       <c r="E6">
-        <v>498.16</v>
+        <v>629.5599999999999</v>
       </c>
       <c r="F6">
-        <v>79.60000000000001</v>
+        <v>69.69999999999999</v>
       </c>
       <c r="G6">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D7">
-        <v>120.905</v>
+        <v>122.724</v>
       </c>
       <c r="E7">
-        <v>483.62</v>
+        <v>613.62</v>
       </c>
       <c r="F7">
-        <v>65.10000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="G7">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>112.44</v>
+        <v>118.924</v>
       </c>
       <c r="E8">
-        <v>449.76</v>
+        <v>594.62</v>
       </c>
       <c r="F8">
-        <v>29.8</v>
+        <v>40.1</v>
       </c>
       <c r="G8">
-        <v>12.8</v>
+        <v>4.2</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>109.72</v>
+        <v>119.204</v>
       </c>
       <c r="E9">
-        <v>438.88</v>
+        <v>596.02</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>39.6</v>
       </c>
       <c r="G9">
-        <v>22.8</v>
+        <v>5.7</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>114.92</v>
+        <v>111.848</v>
       </c>
       <c r="E10">
-        <v>459.68</v>
+        <v>559.24</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="G10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C11">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>110.775</v>
+        <v>98.34</v>
       </c>
       <c r="E11">
-        <v>443.1</v>
+        <v>491.7</v>
       </c>
       <c r="F11">
-        <v>9.6</v>
+        <v>3.2</v>
       </c>
       <c r="G11">
-        <v>38.8</v>
+        <v>51.7</v>
       </c>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2920,19 +2982,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2940,19 +3002,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2960,19 +3022,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2980,19 +3042,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3000,19 +3062,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3020,19 +3082,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3040,13 +3102,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -3063,16 +3125,16 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3080,19 +3142,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3100,10 +3162,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>-8</v>
@@ -3112,7 +3174,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3120,16 +3182,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>93</v>
@@ -3142,10 +3204,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>94</v>
       </c>
@@ -3159,130 +3221,151 @@
         <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>98</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>-4</v>
+      </c>
+      <c r="C2">
+        <v>-2</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>14</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>18</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>-4</v>
-      </c>
-      <c r="C3">
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
         <v>-2</v>
       </c>
-      <c r="D3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>-1</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="E3">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
+      <c r="G6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-1</v>
+      </c>
+      <c r="C7">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>-1</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>-2</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -3298,67 +3381,79 @@
       <c r="E8">
         <v>-6</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8">
+        <v>-5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>-6</v>
+      </c>
+      <c r="C9">
+        <v>-8</v>
+      </c>
+      <c r="D9">
+        <v>-8</v>
+      </c>
+      <c r="E9">
+        <v>-8</v>
+      </c>
+      <c r="F9">
+        <v>-5</v>
+      </c>
+      <c r="G9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>-2</v>
+      </c>
+      <c r="E10">
+        <v>-10</v>
+      </c>
+      <c r="F10">
+        <v>-8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B11">
         <v>-4</v>
       </c>
-      <c r="C9">
+      <c r="C11">
         <v>-11</v>
       </c>
-      <c r="D9">
+      <c r="D11">
         <v>-17</v>
       </c>
-      <c r="E9">
+      <c r="E11">
         <v>-7</v>
       </c>
-      <c r="F9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>-6</v>
-      </c>
-      <c r="C10">
-        <v>-8</v>
-      </c>
-      <c r="D10">
-        <v>-8</v>
-      </c>
-      <c r="E10">
-        <v>-8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>-2</v>
-      </c>
-      <c r="E11">
-        <v>-10</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="F11">
+        <v>-16</v>
+      </c>
+      <c r="G11" t="s">
         <v>93</v>
       </c>
     </row>

--- a/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
+++ b/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="112">
   <si>
     <t>LaPortAuthority</t>
   </si>
@@ -55,22 +55,22 @@
     <t>The Turbanator</t>
   </si>
   <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +142,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,36 +166,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Anthony Rizzo</t>
+  </si>
+  <si>
+    <t>Bridget Cashel</t>
+  </si>
+  <si>
+    <t>Victor Rojas</t>
+  </si>
+  <si>
     <t>Marvin Ta</t>
   </si>
   <si>
+    <t>Maulin Patel</t>
+  </si>
+  <si>
     <t>Chris Carbone</t>
   </si>
   <si>
-    <t>Anthony Rizzo</t>
-  </si>
-  <si>
-    <t>Maulin Patel</t>
+    <t>Alyssa Ianovale</t>
+  </si>
+  <si>
+    <t>Robbie Wilston</t>
   </si>
   <si>
     <t>Kermelos Woldeyes</t>
   </si>
   <si>
-    <t>Victor Rojas</t>
-  </si>
-  <si>
-    <t>Robbie Wilston</t>
-  </si>
-  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Bridget Cashel</t>
-  </si>
-  <si>
-    <t>Alyssa Ianovale</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -217,49 +220,55 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>10.7-3.2-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.5-0.1</t>
-  </si>
-  <si>
-    <t>8.1-5.8-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>4.1-9.8-0.1</t>
-  </si>
-  <si>
-    <t>4.0-9.9-0.1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>10.5-3.4-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>8.3-5.6-0.1</t>
+  </si>
+  <si>
+    <t>7.9-6.0-0.1</t>
+  </si>
+  <si>
+    <t>7.0-6.9-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.4-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.5-0.1</t>
+  </si>
+  <si>
+    <t>4.2-9.7-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>10-4</t>
+    <t>9-5</t>
   </si>
   <si>
     <t>8-6</t>
@@ -271,6 +280,9 @@
     <t>6-8</t>
   </si>
   <si>
+    <t>5-9</t>
+  </si>
+  <si>
     <t>4-10</t>
   </si>
   <si>
@@ -283,28 +295,31 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓7</t>
+  </si>
+  <si>
     <t>↑1</t>
   </si>
   <si>
     <t>↓6</t>
   </si>
   <si>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
     <t>↑4</t>
   </si>
   <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓9</t>
+    <t>↓8</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -320,6 +335,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -741,22 +759,22 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -776,10 +794,10 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -808,13 +826,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -823,7 +841,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -835,7 +853,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -846,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -855,13 +873,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
@@ -870,7 +888,7 @@
         <v>10</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -878,31 +896,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
@@ -916,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
@@ -937,7 +955,7 @@
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K7" t="s">
         <v>10</v>
@@ -951,31 +969,31 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
         <v>13</v>
       </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" t="s">
-        <v>14</v>
-      </c>
       <c r="J8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -986,16 +1004,16 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -1010,7 +1028,7 @@
         <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1018,34 +1036,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1053,7 +1071,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -1062,16 +1080,16 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
         <v>11</v>
@@ -1080,7 +1098,7 @@
         <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1090,30 +1108,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1147,25 +1165,25 @@
         <v>1</v>
       </c>
       <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
       <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
       <c r="F3">
-        <v>18</v>
+        <v>-12</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1173,25 +1191,25 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>-8</v>
-      </c>
       <c r="F4">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1199,25 +1217,25 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>-8</v>
+      </c>
+      <c r="F5">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>-2</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
       <c r="G5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1225,25 +1243,25 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>-2</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>-5</v>
-      </c>
       <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
         <v>6</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1251,25 +1269,103 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
       <c r="E7">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>-2</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>-2</v>
+      </c>
+      <c r="F10">
+        <v>-4</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1301,10 +1397,10 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1315,7 +1411,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1326,13 +1422,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1340,13 +1436,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1357,7 +1453,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -1371,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1382,13 +1478,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1396,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1410,13 +1506,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1424,10 +1520,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1465,10 +1561,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="D2">
-        <v>-0.2000000000000002</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1479,13 +1575,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D3">
-        <v>0.2000000000000002</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1496,16 +1592,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="D4">
-        <v>-0.8999999999999999</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1516,10 +1612,10 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D5">
-        <v>-0.1000000000000001</v>
+        <v>-0.7999999999999998</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1530,16 +1626,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="D6">
-        <v>0.6000000000000001</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1547,16 +1643,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>2.3</v>
-      </c>
       <c r="D7">
-        <v>0.2999999999999998</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1564,13 +1660,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="D8">
-        <v>0.2000000000000002</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1581,16 +1677,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1598,16 +1694,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1615,16 +1711,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="D11">
-        <v>-0.6000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1680,19 +1776,19 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>74.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="C2">
-        <v>16.5</v>
+        <v>15.3</v>
       </c>
       <c r="D2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="E2">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="G2">
         <v>0.3</v>
@@ -1718,110 +1814,110 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>13.3</v>
+        <v>10.4</v>
       </c>
       <c r="C3">
-        <v>33.2</v>
+        <v>31.2</v>
       </c>
       <c r="D3">
-        <v>25.2</v>
+        <v>22.2</v>
       </c>
       <c r="E3">
-        <v>13.9</v>
+        <v>18.4</v>
       </c>
       <c r="F3">
-        <v>8.9</v>
+        <v>10.1</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H3">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>98.5</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="C4">
-        <v>25.3</v>
+        <v>21.8</v>
       </c>
       <c r="D4">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="E4">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="F4">
-        <v>11.9</v>
+        <v>12.8</v>
       </c>
       <c r="G4">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="H4">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J4">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K4">
         <v>0.1</v>
       </c>
       <c r="L4">
-        <v>95.2</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="C5">
-        <v>16.8</v>
+        <v>21.5</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>22.2</v>
+        <v>20.5</v>
       </c>
       <c r="F5">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="G5">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J5">
         <v>0.7</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
         <v>92.09999999999999</v>
@@ -1829,197 +1925,197 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C6">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="D6">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="E6">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="F6">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="G6">
-        <v>21.1</v>
+        <v>17.6</v>
       </c>
       <c r="H6">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="I6">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>69.7</v>
+        <v>71.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C7">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>5.2</v>
+        <v>7.7</v>
       </c>
       <c r="E7">
-        <v>10.4</v>
+        <v>14.2</v>
       </c>
       <c r="F7">
-        <v>17.4</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>19.2</v>
+        <v>20.3</v>
       </c>
       <c r="H7">
-        <v>22</v>
+        <v>15.3</v>
       </c>
       <c r="I7">
-        <v>15.6</v>
+        <v>10.1</v>
       </c>
       <c r="J7">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="K7">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="L7">
-        <v>54.7</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="E8">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="F8">
-        <v>11.8</v>
+        <v>6.8</v>
       </c>
       <c r="G8">
-        <v>18.7</v>
+        <v>16.2</v>
       </c>
       <c r="H8">
-        <v>22.6</v>
+        <v>19.4</v>
       </c>
       <c r="I8">
-        <v>21.8</v>
+        <v>20.3</v>
       </c>
       <c r="J8">
-        <v>11.3</v>
+        <v>19.1</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>12.7</v>
       </c>
       <c r="L8">
-        <v>40.1</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="E9">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="F9">
-        <v>12.9</v>
+        <v>6.9</v>
       </c>
       <c r="G9">
+        <v>11.2</v>
+      </c>
+      <c r="H9">
+        <v>17.1</v>
+      </c>
+      <c r="I9">
+        <v>22.2</v>
+      </c>
+      <c r="J9">
+        <v>23.4</v>
+      </c>
+      <c r="K9">
         <v>15.9</v>
       </c>
-      <c r="H9">
-        <v>19.7</v>
-      </c>
-      <c r="I9">
-        <v>22.4</v>
-      </c>
-      <c r="J9">
-        <v>12.6</v>
-      </c>
-      <c r="K9">
-        <v>5.7</v>
-      </c>
       <c r="L9">
-        <v>39.6</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="E10">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="F10">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="G10">
-        <v>4.5</v>
+        <v>10.2</v>
       </c>
       <c r="H10">
-        <v>5.7</v>
+        <v>14.2</v>
       </c>
       <c r="I10">
-        <v>16.4</v>
+        <v>19.4</v>
       </c>
       <c r="J10">
-        <v>36.9</v>
+        <v>23.8</v>
       </c>
       <c r="K10">
-        <v>34</v>
+        <v>21.6</v>
       </c>
       <c r="L10">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2028,31 +2124,31 @@
         <v>0.1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E11">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="G11">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="H11">
-        <v>5.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I11">
-        <v>11.1</v>
+        <v>14.3</v>
       </c>
       <c r="J11">
-        <v>28.8</v>
+        <v>23.4</v>
       </c>
       <c r="K11">
-        <v>51.7</v>
+        <v>45.2</v>
       </c>
       <c r="L11">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -2062,10 +2158,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
@@ -2084,8 +2180,11 @@
       <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2093,7 +2192,7 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>94.19999999999999</v>
+        <v>93.10000000000001</v>
       </c>
       <c r="D2">
         <v>99.5</v>
@@ -2102,217 +2201,247 @@
         <v>99.59999999999999</v>
       </c>
       <c r="F2">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G2">
+        <v>99.8</v>
+      </c>
+      <c r="H2">
         <v>100</v>
       </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C3">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D3">
-        <v>95.19999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="E3">
-        <v>87.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F3">
-        <v>97.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G3">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="H3">
+        <v>97.09999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>80.30000000000001</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="E4">
+        <v>97.5</v>
+      </c>
+      <c r="F4">
+        <v>94.69999999999999</v>
+      </c>
+      <c r="G4">
+        <v>95</v>
+      </c>
+      <c r="H4">
+        <v>94.09999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>99.5</v>
+      </c>
+      <c r="C5">
+        <v>77.5</v>
+      </c>
+      <c r="D5">
+        <v>81.8</v>
+      </c>
+      <c r="E5">
+        <v>61.8</v>
+      </c>
+      <c r="F5">
+        <v>65.8</v>
+      </c>
+      <c r="G5">
+        <v>93</v>
+      </c>
+      <c r="H5">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>3.2</v>
-      </c>
-      <c r="C4">
-        <v>26.4</v>
-      </c>
-      <c r="D4">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="E4">
-        <v>86.2</v>
-      </c>
-      <c r="F4">
-        <v>95.5</v>
-      </c>
-      <c r="G4">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5">
-        <v>98.8</v>
-      </c>
-      <c r="E5">
-        <v>98</v>
-      </c>
-      <c r="F5">
-        <v>95.19999999999999</v>
-      </c>
-      <c r="G5">
-        <v>93.40000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B6">
-        <v>99.5</v>
+        <v>1.2</v>
       </c>
       <c r="C6">
-        <v>79</v>
+        <v>27.3</v>
       </c>
       <c r="D6">
-        <v>80</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E6">
-        <v>63.1</v>
+        <v>83.89999999999999</v>
       </c>
       <c r="F6">
-        <v>68.30000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="G6">
-        <v>72.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>70.39999999999999</v>
+      </c>
+      <c r="H6">
+        <v>71.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>99.7</v>
+      </c>
+      <c r="C7">
+        <v>90.5</v>
+      </c>
+      <c r="D7">
+        <v>55.60000000000001</v>
+      </c>
+      <c r="E7">
+        <v>24.8</v>
+      </c>
+      <c r="F7">
+        <v>39.6</v>
+      </c>
+      <c r="G7">
+        <v>63.9</v>
+      </c>
+      <c r="H7">
+        <v>68.60000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7">
-        <v>29.4</v>
-      </c>
-      <c r="C7">
-        <v>3.4</v>
-      </c>
-      <c r="D7">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="E7">
-        <v>23.1</v>
-      </c>
-      <c r="F7">
-        <v>57.49999999999999</v>
-      </c>
-      <c r="G7">
-        <v>58.59999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="B8">
-        <v>99.59999999999999</v>
+        <v>32.2</v>
       </c>
       <c r="C8">
-        <v>90.7</v>
+        <v>4.2</v>
       </c>
       <c r="D8">
-        <v>55.60000000000001</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>23.3</v>
+        <v>24.8</v>
       </c>
       <c r="F8">
-        <v>42.1</v>
+        <v>58.2</v>
       </c>
       <c r="G8">
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>27.2</v>
+      </c>
+      <c r="H8">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B9">
-        <v>36.2</v>
+        <v>30.2</v>
       </c>
       <c r="C9">
-        <v>93.89999999999999</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="D9">
-        <v>68.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E9">
-        <v>89.7</v>
+        <v>89.8</v>
       </c>
       <c r="F9">
-        <v>35.9</v>
+        <v>37.5</v>
       </c>
       <c r="G9">
-        <v>32.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>29.7</v>
+      </c>
+      <c r="H9">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>57.49999999999999</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>0.3</v>
+      </c>
+      <c r="E10">
+        <v>19.6</v>
+      </c>
+      <c r="F10">
+        <v>3.4</v>
+      </c>
+      <c r="G10">
+        <v>16.5</v>
+      </c>
+      <c r="H10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="C10">
-        <v>15.6</v>
-      </c>
-      <c r="D10">
-        <v>34.1</v>
-      </c>
-      <c r="E10">
-        <v>9.6</v>
-      </c>
-      <c r="F10">
-        <v>4.9</v>
-      </c>
-      <c r="G10">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>52.1</v>
-      </c>
       <c r="C11">
-        <v>5.600000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>31.9</v>
       </c>
       <c r="E11">
-        <v>20.3</v>
+        <v>11.6</v>
       </c>
       <c r="F11">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="G11">
-        <v>3.8</v>
+        <v>6.9</v>
+      </c>
+      <c r="H11">
+        <v>6.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2330,25 +2459,25 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2356,28 +2485,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2">
+        <v>115.84</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>121.7</v>
+      </c>
+      <c r="G2">
+        <v>0.5</v>
+      </c>
+      <c r="H2">
+        <v>1.5</v>
+      </c>
+      <c r="I2">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2">
-        <v>98.34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>126.14</v>
-      </c>
-      <c r="G2">
-        <v>0.511</v>
-      </c>
-      <c r="H2">
-        <v>1.8</v>
-      </c>
-      <c r="I2">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2385,28 +2514,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>119.2</v>
+        <v>125.46</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>123.82</v>
+        <v>121.7</v>
       </c>
       <c r="G3">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2414,28 +2543,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4">
-        <v>122.72</v>
+        <v>116.73</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>123.43</v>
+        <v>124.16</v>
       </c>
       <c r="G4">
-        <v>0.511</v>
+        <v>0.521</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2443,28 +2572,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>129.89</v>
+        <v>104.89</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>122.63</v>
+        <v>124.16</v>
       </c>
       <c r="G5">
-        <v>0.467</v>
+        <v>0.521</v>
       </c>
       <c r="H5">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2472,28 +2601,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>111.85</v>
+        <v>128.24</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>124.64</v>
+        <v>120.86</v>
       </c>
       <c r="G6">
-        <v>0.533</v>
+        <v>0.479</v>
       </c>
       <c r="H6">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2501,28 +2630,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7">
-        <v>118.92</v>
+        <v>119.77</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>123.85</v>
+        <v>120.86</v>
       </c>
       <c r="G7">
-        <v>0.511</v>
+        <v>0.479</v>
       </c>
       <c r="H7">
-        <v>-0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2530,28 +2659,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>144.51</v>
+        <v>120.64</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>121.01</v>
+        <v>119.46</v>
       </c>
       <c r="G8">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H8">
         <v>-0.6</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2559,28 +2688,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9">
-        <v>125.91</v>
+        <v>138.58</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>123.08</v>
+        <v>119.46</v>
       </c>
       <c r="G9">
-        <v>0.511</v>
+        <v>0.458</v>
       </c>
       <c r="H9">
         <v>-0.6</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2588,28 +2717,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>130.17</v>
+        <v>113.4</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F10">
-        <v>122.6</v>
+        <v>121.27</v>
       </c>
       <c r="G10">
-        <v>0.489</v>
+        <v>0.542</v>
       </c>
       <c r="H10">
-        <v>-0.8</v>
+        <v>-2.5</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2617,28 +2746,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11">
-        <v>132.08</v>
+        <v>131.35</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>122.39</v>
+        <v>121.27</v>
       </c>
       <c r="G11">
-        <v>0.489</v>
+        <v>0.542</v>
       </c>
       <c r="H11">
-        <v>-1.3</v>
+        <v>-2.5</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2656,28 +2785,28 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2685,16 +2814,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>144.508</v>
+        <v>138.5766666666667</v>
       </c>
       <c r="E2">
-        <v>722.54</v>
+        <v>831.4599999999999</v>
       </c>
       <c r="F2">
         <v>99.90000000000001</v>
@@ -2703,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2714,260 +2843,260 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>129.888</v>
+        <v>128.24</v>
       </c>
       <c r="E3">
-        <v>649.4400000000001</v>
+        <v>769.4400000000001</v>
       </c>
       <c r="F3">
-        <v>98.5</v>
+        <v>96.5</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>132.076</v>
+        <v>125.46</v>
       </c>
       <c r="E4">
-        <v>660.38</v>
+        <v>752.76</v>
       </c>
       <c r="F4">
-        <v>95.19999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G4">
         <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>130.172</v>
+        <v>131.35</v>
       </c>
       <c r="E5">
-        <v>650.86</v>
+        <v>788.0999999999999</v>
       </c>
       <c r="F5">
         <v>92.10000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>125.912</v>
+        <v>120.6433333333333</v>
       </c>
       <c r="E6">
-        <v>629.5599999999999</v>
+        <v>723.86</v>
       </c>
       <c r="F6">
-        <v>69.69999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G6">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>122.724</v>
+        <v>119.77</v>
       </c>
       <c r="E7">
-        <v>613.62</v>
+        <v>718.62</v>
       </c>
       <c r="F7">
-        <v>54.7</v>
+        <v>67.60000000000001</v>
       </c>
       <c r="G7">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>118.924</v>
+        <v>115.8366666666667</v>
       </c>
       <c r="E8">
-        <v>594.62</v>
+        <v>695.02</v>
       </c>
       <c r="F8">
-        <v>40.1</v>
+        <v>28.5</v>
       </c>
       <c r="G8">
-        <v>4.2</v>
+        <v>12.7</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>119.204</v>
+        <v>116.7333333333333</v>
       </c>
       <c r="E9">
-        <v>596.02</v>
+        <v>700.4</v>
       </c>
       <c r="F9">
-        <v>39.6</v>
+        <v>21.4</v>
       </c>
       <c r="G9">
-        <v>5.7</v>
+        <v>15.9</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>67</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>111.848</v>
+        <v>104.8866666666667</v>
       </c>
       <c r="E10">
-        <v>559.24</v>
+        <v>629.3199999999999</v>
       </c>
       <c r="F10">
-        <v>7.000000000000001</v>
+        <v>21</v>
       </c>
       <c r="G10">
-        <v>34</v>
+        <v>21.6</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D11">
-        <v>98.34</v>
+        <v>113.3966666666667</v>
       </c>
       <c r="E11">
-        <v>491.7</v>
+        <v>680.38</v>
       </c>
       <c r="F11">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="G11">
-        <v>51.7</v>
+        <v>45.2</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2985,16 +3114,16 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3002,19 +3131,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3022,19 +3151,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3">
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3042,7 +3171,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>53</v>
@@ -3051,10 +3180,10 @@
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3062,19 +3191,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3082,19 +3211,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3102,19 +3231,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3125,16 +3254,16 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3142,19 +3271,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3162,19 +3291,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3182,19 +3311,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3204,168 +3333,189 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>104</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>-1</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
         <v>-4</v>
       </c>
-      <c r="C2">
+      <c r="C4">
         <v>-2</v>
       </c>
-      <c r="D2">
+      <c r="D4">
         <v>4</v>
       </c>
-      <c r="E2">
+      <c r="E4">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>14</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>13</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
         <v>-2</v>
       </c>
-      <c r="D5">
+      <c r="D7">
         <v>0</v>
       </c>
-      <c r="E5">
+      <c r="E7">
         <v>-1</v>
       </c>
-      <c r="F5">
+      <c r="F7">
         <v>5</v>
       </c>
-      <c r="G5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>-1</v>
-      </c>
-      <c r="C7">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -3384,77 +3534,89 @@
       <c r="F8">
         <v>-5</v>
       </c>
-      <c r="G8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="G8">
+        <v>-2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>-2</v>
+      </c>
+      <c r="E9">
+        <v>-10</v>
+      </c>
+      <c r="F9">
+        <v>-8</v>
+      </c>
+      <c r="G9">
+        <v>-4</v>
+      </c>
+      <c r="H9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>-4</v>
+      </c>
+      <c r="C10">
+        <v>-11</v>
+      </c>
+      <c r="D10">
+        <v>-17</v>
+      </c>
+      <c r="E10">
+        <v>-7</v>
+      </c>
+      <c r="F10">
+        <v>-16</v>
+      </c>
+      <c r="G10">
+        <v>-12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9">
+      <c r="B11">
         <v>-6</v>
       </c>
-      <c r="C9">
+      <c r="C11">
         <v>-8</v>
       </c>
-      <c r="D9">
+      <c r="D11">
         <v>-8</v>
       </c>
-      <c r="E9">
+      <c r="E11">
         <v>-8</v>
       </c>
-      <c r="F9">
+      <c r="F11">
         <v>-5</v>
       </c>
-      <c r="G9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>-2</v>
-      </c>
-      <c r="E10">
-        <v>-10</v>
-      </c>
-      <c r="F10">
-        <v>-8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>-4</v>
-      </c>
-      <c r="C11">
-        <v>-11</v>
-      </c>
-      <c r="D11">
-        <v>-17</v>
-      </c>
-      <c r="E11">
-        <v>-7</v>
-      </c>
-      <c r="F11">
-        <v>-16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>93</v>
+      <c r="G11">
+        <v>-13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
+++ b/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="114">
   <si>
     <t>LaPortAuthority</t>
   </si>
@@ -55,22 +55,22 @@
     <t>The Turbanator</t>
   </si>
   <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -145,6 +145,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -169,6 +172,9 @@
     <t>Anthony Rizzo</t>
   </si>
   <si>
+    <t>Maulin Patel</t>
+  </si>
+  <si>
     <t>Bridget Cashel</t>
   </si>
   <si>
@@ -178,18 +184,15 @@
     <t>Marvin Ta</t>
   </si>
   <si>
-    <t>Maulin Patel</t>
+    <t>Robbie Wilston</t>
+  </si>
+  <si>
+    <t>Alyssa Ianovale</t>
   </si>
   <si>
     <t>Chris Carbone</t>
   </si>
   <si>
-    <t>Alyssa Ianovale</t>
-  </si>
-  <si>
-    <t>Robbie Wilston</t>
-  </si>
-  <si>
     <t>Kermelos Woldeyes</t>
   </si>
   <si>
@@ -220,49 +223,52 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>10.5-3.4-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>8.3-5.6-0.1</t>
-  </si>
-  <si>
-    <t>7.9-6.0-0.1</t>
-  </si>
-  <si>
-    <t>7.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.4-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.5-0.1</t>
-  </si>
-  <si>
-    <t>4.2-9.7-0.1</t>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>11.3-2.7-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.4-0.1</t>
+  </si>
+  <si>
+    <t>8.0-6.0-0.1</t>
+  </si>
+  <si>
+    <t>7.3-6.6-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>6.1-7.8-0.1</t>
+  </si>
+  <si>
+    <t>5.3-8.7-0.1</t>
+  </si>
+  <si>
+    <t>4.6-9.3-0.1</t>
+  </si>
+  <si>
+    <t>3.7-10.2-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -295,31 +301,28 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑8</t>
-  </si>
-  <si>
     <t>↑6</t>
   </si>
   <si>
-    <t>↓7</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓6</t>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓4</t>
   </si>
   <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓8</t>
+    <t>0</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -338,6 +341,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -759,10 +765,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -777,13 +783,13 @@
         <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -800,25 +806,25 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -826,13 +832,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -844,7 +850,7 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
         <v>13</v>
@@ -853,7 +859,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -861,34 +867,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -899,31 +905,31 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" t="s">
+      <c r="K6" t="s">
         <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -931,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -946,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
         <v>10</v>
@@ -958,7 +964,7 @@
         <v>11</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -975,25 +981,25 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
         <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1007,28 +1013,28 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
       </c>
       <c r="J9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" t="s">
         <v>11</v>
-      </c>
-      <c r="K9" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1036,34 +1042,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
         <v>14</v>
       </c>
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1071,34 +1077,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>12</v>
-      </c>
-      <c r="I11" t="s">
-        <v>11</v>
       </c>
       <c r="J11" t="s">
         <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1108,30 +1114,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1217,25 +1223,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
         <v>2</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1243,25 +1249,25 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>-8</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>-2</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
       <c r="G6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1269,25 +1275,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>-16</v>
       </c>
       <c r="F7">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1295,25 +1301,25 @@
         <v>6</v>
       </c>
       <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1321,22 +1327,22 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
       <c r="E9">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" t="s">
         <v>1</v>
@@ -1350,22 +1356,48 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>-2</v>
+      </c>
+      <c r="F11">
         <v>2</v>
       </c>
-      <c r="E10">
-        <v>-2</v>
-      </c>
-      <c r="F10">
-        <v>-4</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10" t="s">
-        <v>2</v>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1397,10 +1429,10 @@
         <v>4</v>
       </c>
       <c r="C2">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1411,10 +1443,10 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1425,10 +1457,10 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1439,10 +1471,10 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1450,13 +1482,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1464,13 +1496,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1478,10 +1510,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1492,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1509,7 +1541,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1523,7 +1555,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1561,7 +1593,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="D2">
         <v>-0.7000000000000002</v>
@@ -1575,16 +1607,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="D3">
-        <v>-0.3999999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1592,16 +1624,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="D4">
-        <v>0.6000000000000001</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1612,13 +1644,13 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="D5">
-        <v>-0.7999999999999998</v>
+        <v>-1.2</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1629,13 +1661,13 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="D6">
-        <v>0.2000000000000002</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1643,16 +1675,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1660,13 +1692,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D8">
-        <v>0.6000000000000001</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1677,16 +1709,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="D9">
-        <v>-0.7000000000000002</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1694,13 +1726,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D10">
-        <v>0.1000000000000001</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1714,13 +1746,13 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D11">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1776,25 +1808,25 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>75.7</v>
+        <v>93.8</v>
       </c>
       <c r="C2">
-        <v>15.3</v>
+        <v>4.4</v>
       </c>
       <c r="D2">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="E2">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="F2">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1806,36 +1838,36 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>10.4</v>
+        <v>2.9</v>
       </c>
       <c r="C3">
-        <v>31.2</v>
+        <v>34.8</v>
       </c>
       <c r="D3">
-        <v>22.2</v>
+        <v>23.4</v>
       </c>
       <c r="E3">
-        <v>18.4</v>
+        <v>15.5</v>
       </c>
       <c r="F3">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
       <c r="G3">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="I3">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J3">
         <v>0.1</v>
@@ -1844,45 +1876,45 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="C4">
-        <v>21.8</v>
+        <v>24.1</v>
       </c>
       <c r="D4">
-        <v>25.7</v>
+        <v>19.3</v>
       </c>
       <c r="E4">
-        <v>18.7</v>
+        <v>20.1</v>
       </c>
       <c r="F4">
-        <v>12.8</v>
+        <v>15.8</v>
       </c>
       <c r="G4">
-        <v>7.7</v>
+        <v>10.4</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J4">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>94.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1890,113 +1922,113 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="C5">
-        <v>21.5</v>
+        <v>14.3</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>18.9</v>
       </c>
       <c r="E5">
-        <v>20.5</v>
+        <v>19.1</v>
       </c>
       <c r="F5">
-        <v>13.3</v>
+        <v>18.5</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>14.8</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="K5">
         <v>0.1</v>
       </c>
       <c r="L5">
-        <v>92.09999999999999</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C6">
-        <v>5.7</v>
+        <v>11.8</v>
       </c>
       <c r="D6">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="E6">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="F6">
-        <v>19.4</v>
+        <v>18.6</v>
       </c>
       <c r="G6">
-        <v>17.6</v>
+        <v>18.2</v>
       </c>
       <c r="H6">
-        <v>13.9</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L6">
-        <v>71.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>0.4</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D7">
-        <v>7.7</v>
+        <v>13.6</v>
       </c>
       <c r="E7">
-        <v>14.2</v>
+        <v>19.8</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>18.6</v>
       </c>
       <c r="G7">
-        <v>20.3</v>
+        <v>16.6</v>
       </c>
       <c r="H7">
-        <v>15.3</v>
+        <v>13.5</v>
       </c>
       <c r="I7">
-        <v>10.1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="K7">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="L7">
-        <v>67.59999999999999</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2007,110 +2039,110 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="D8">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="E8">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="F8">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="G8">
-        <v>16.2</v>
+        <v>18.3</v>
       </c>
       <c r="H8">
-        <v>19.4</v>
+        <v>27.5</v>
       </c>
       <c r="I8">
-        <v>20.3</v>
+        <v>18.8</v>
       </c>
       <c r="J8">
-        <v>19.1</v>
+        <v>12</v>
       </c>
       <c r="K8">
-        <v>12.7</v>
+        <v>3.5</v>
       </c>
       <c r="L8">
-        <v>28.5</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="E9">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F9">
-        <v>6.9</v>
+        <v>3.8</v>
       </c>
       <c r="G9">
-        <v>11.2</v>
+        <v>6.4</v>
       </c>
       <c r="H9">
-        <v>17.1</v>
+        <v>14.2</v>
       </c>
       <c r="I9">
-        <v>22.2</v>
+        <v>27.9</v>
       </c>
       <c r="J9">
-        <v>23.4</v>
+        <v>27.7</v>
       </c>
       <c r="K9">
-        <v>15.9</v>
+        <v>17.2</v>
       </c>
       <c r="L9">
-        <v>21.4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D10">
+        <v>0.3</v>
+      </c>
+      <c r="E10">
         <v>1.3</v>
       </c>
-      <c r="E10">
-        <v>3.1</v>
-      </c>
       <c r="F10">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="G10">
-        <v>10.2</v>
+        <v>5.6</v>
       </c>
       <c r="H10">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="I10">
-        <v>19.4</v>
+        <v>24</v>
       </c>
       <c r="J10">
-        <v>23.8</v>
+        <v>29.5</v>
       </c>
       <c r="K10">
-        <v>21.6</v>
+        <v>23.7</v>
       </c>
       <c r="L10">
-        <v>21</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2121,34 +2153,34 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="F11">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="G11">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="H11">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="I11">
-        <v>14.3</v>
+        <v>12.8</v>
       </c>
       <c r="J11">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="K11">
-        <v>45.2</v>
+        <v>54.9</v>
       </c>
       <c r="L11">
-        <v>7.8</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -2158,10 +2190,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
@@ -2183,8 +2215,11 @@
       <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -2192,233 +2227,260 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>93.10000000000001</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="D2">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E2">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F2">
         <v>99.90000000000001</v>
       </c>
       <c r="G2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>99.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="C3">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D3">
+        <v>98</v>
+      </c>
+      <c r="E3">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="F3">
         <v>95.3</v>
       </c>
-      <c r="E3">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="F3">
-        <v>98.59999999999999</v>
-      </c>
       <c r="G3">
-        <v>97.59999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H3">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I3">
         <v>97.09999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>80.30000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D4">
-        <v>98.59999999999999</v>
+        <v>57.09999999999999</v>
       </c>
       <c r="E4">
-        <v>97.5</v>
+        <v>24.4</v>
       </c>
       <c r="F4">
-        <v>94.69999999999999</v>
+        <v>41.6</v>
       </c>
       <c r="G4">
-        <v>95</v>
+        <v>66.2</v>
       </c>
       <c r="H4">
-        <v>94.09999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>90.60000000000001</v>
+      </c>
+      <c r="I4">
+        <v>93.10000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>99.5</v>
+        <v>99.8</v>
       </c>
       <c r="C5">
-        <v>77.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D5">
-        <v>81.8</v>
+        <v>81</v>
       </c>
       <c r="E5">
-        <v>61.8</v>
+        <v>60.4</v>
       </c>
       <c r="F5">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="G5">
-        <v>93</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="H5">
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I5">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C6">
+        <v>90.10000000000001</v>
+      </c>
+      <c r="D6">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E6">
+        <v>87.3</v>
+      </c>
+      <c r="F6">
+        <v>97.8</v>
+      </c>
+      <c r="G6">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="H6">
+        <v>84.8</v>
+      </c>
+      <c r="I6">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>1.2</v>
-      </c>
-      <c r="C6">
+      <c r="B7">
+        <v>2.3</v>
+      </c>
+      <c r="C7">
         <v>27.3</v>
       </c>
-      <c r="D6">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="E6">
-        <v>83.89999999999999</v>
-      </c>
-      <c r="F6">
-        <v>95.8</v>
-      </c>
-      <c r="G6">
-        <v>70.39999999999999</v>
-      </c>
-      <c r="H6">
-        <v>71.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>99.7</v>
-      </c>
-      <c r="C7">
-        <v>90.5</v>
-      </c>
       <c r="D7">
-        <v>55.60000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="E7">
-        <v>24.8</v>
+        <v>82.69999999999999</v>
       </c>
       <c r="F7">
-        <v>39.6</v>
+        <v>96.2</v>
       </c>
       <c r="G7">
-        <v>63.9</v>
+        <v>69.3</v>
       </c>
       <c r="H7">
-        <v>68.60000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>78.2</v>
+      </c>
+      <c r="I7">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B8">
-        <v>32.2</v>
+        <v>31.5</v>
       </c>
       <c r="C8">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E8">
-        <v>24.8</v>
+        <v>25.9</v>
       </c>
       <c r="F8">
-        <v>58.2</v>
+        <v>56.39999999999999</v>
       </c>
       <c r="G8">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="H8">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>40.7</v>
+      </c>
+      <c r="I8">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>53.40000000000001</v>
+      </c>
+      <c r="C9">
+        <v>5.3</v>
+      </c>
+      <c r="D9">
+        <v>0.2</v>
+      </c>
+      <c r="E9">
+        <v>19.8</v>
+      </c>
+      <c r="F9">
+        <v>4.3</v>
+      </c>
+      <c r="G9">
+        <v>18.6</v>
+      </c>
+      <c r="H9">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I9">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B9">
-        <v>30.2</v>
-      </c>
-      <c r="C9">
+      <c r="B10">
+        <v>31.6</v>
+      </c>
+      <c r="C10">
         <v>94.39999999999999</v>
       </c>
-      <c r="D9">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="E9">
-        <v>89.8</v>
-      </c>
-      <c r="F9">
-        <v>37.5</v>
-      </c>
-      <c r="G9">
-        <v>29.7</v>
-      </c>
-      <c r="H9">
-        <v>25.1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>57.49999999999999</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>70.8</v>
       </c>
       <c r="E10">
-        <v>19.6</v>
+        <v>90.3</v>
       </c>
       <c r="F10">
-        <v>3.4</v>
+        <v>36</v>
       </c>
       <c r="G10">
-        <v>16.5</v>
+        <v>27.6</v>
       </c>
       <c r="H10">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I10">
+        <v>9.700000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -2426,22 +2488,25 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="D11">
-        <v>31.9</v>
+        <v>33.6</v>
       </c>
       <c r="E11">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="F11">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="G11">
-        <v>6.9</v>
+        <v>5.800000000000001</v>
       </c>
       <c r="H11">
-        <v>6.800000000000001</v>
+        <v>2.9</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2459,25 +2524,25 @@
         <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2488,25 +2553,25 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>115.84</v>
+        <v>114.52</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>121.7</v>
+        <v>119.45</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="H2">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2514,28 +2579,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>125.46</v>
+        <v>120.15</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>121.7</v>
+        <v>119.35</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2543,28 +2608,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>116.73</v>
+        <v>122.44</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>124.16</v>
+        <v>120.57</v>
       </c>
       <c r="G4">
-        <v>0.521</v>
+        <v>0.51</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2572,28 +2637,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>104.89</v>
+        <v>112.29</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5">
-        <v>124.16</v>
+        <v>122.43</v>
       </c>
       <c r="G5">
-        <v>0.521</v>
+        <v>0.51</v>
       </c>
       <c r="H5">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2601,28 +2666,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>128.24</v>
+        <v>101.52</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>120.86</v>
+        <v>119.58</v>
       </c>
       <c r="G6">
-        <v>0.479</v>
+        <v>0.49</v>
       </c>
       <c r="H6">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2630,28 +2695,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>119.77</v>
+        <v>142.38</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>120.86</v>
+        <v>118.84</v>
       </c>
       <c r="G7">
-        <v>0.479</v>
+        <v>0.449</v>
       </c>
       <c r="H7">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2662,25 +2727,25 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>120.64</v>
+        <v>117.45</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>119.46</v>
+        <v>117.61</v>
       </c>
       <c r="G8">
-        <v>0.458</v>
+        <v>0.49</v>
       </c>
       <c r="H8">
-        <v>-0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2688,28 +2753,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>123.09</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>117.25</v>
+      </c>
+      <c r="G9">
+        <v>0.49</v>
+      </c>
+      <c r="H9">
+        <v>-2.4</v>
+      </c>
+      <c r="I9">
         <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9">
-        <v>138.58</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9">
-        <v>119.46</v>
-      </c>
-      <c r="G9">
-        <v>0.458</v>
-      </c>
-      <c r="H9">
-        <v>-0.6</v>
-      </c>
-      <c r="I9">
-        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2720,25 +2785,25 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>113.4</v>
+        <v>110.15</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>121.27</v>
+        <v>119.48</v>
       </c>
       <c r="G10">
-        <v>0.542</v>
+        <v>0.551</v>
       </c>
       <c r="H10">
-        <v>-2.5</v>
+        <v>-3.9</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2749,25 +2814,25 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>131.35</v>
+        <v>129.26</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>121.27</v>
+        <v>118.68</v>
       </c>
       <c r="G11">
-        <v>0.542</v>
+        <v>0.551</v>
       </c>
       <c r="H11">
-        <v>-2.5</v>
+        <v>-4</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2785,28 +2850,28 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2814,86 +2879,86 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D2">
-        <v>138.5766666666667</v>
+        <v>142.3771428571428</v>
       </c>
       <c r="E2">
-        <v>831.4599999999999</v>
+        <v>996.6399999999999</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>128.24</v>
+        <v>122.44</v>
       </c>
       <c r="E3">
-        <v>769.4400000000001</v>
+        <v>857.0799999999999</v>
       </c>
       <c r="F3">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4">
-        <v>125.46</v>
+        <v>123.0942857142857</v>
       </c>
       <c r="E4">
-        <v>752.76</v>
+        <v>861.66</v>
       </c>
       <c r="F4">
-        <v>94.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2901,86 +2966,86 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D5">
-        <v>131.35</v>
+        <v>129.2571428571428</v>
       </c>
       <c r="E5">
-        <v>788.0999999999999</v>
+        <v>904.8</v>
       </c>
       <c r="F5">
-        <v>92.10000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="G5">
         <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D6">
-        <v>120.6433333333333</v>
+        <v>120.1514285714286</v>
       </c>
       <c r="E6">
-        <v>723.86</v>
+        <v>841.0600000000001</v>
       </c>
       <c r="F6">
-        <v>71.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D7">
-        <v>119.77</v>
+        <v>117.4514285714286</v>
       </c>
       <c r="E7">
-        <v>718.62</v>
+        <v>822.16</v>
       </c>
       <c r="F7">
-        <v>67.60000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="G7">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2988,86 +3053,86 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D8">
-        <v>115.8366666666667</v>
+        <v>114.52</v>
       </c>
       <c r="E8">
-        <v>695.02</v>
+        <v>801.64</v>
       </c>
       <c r="F8">
-        <v>28.5</v>
+        <v>38.2</v>
       </c>
       <c r="G8">
-        <v>12.7</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D9">
-        <v>116.7333333333333</v>
+        <v>101.5171428571428</v>
       </c>
       <c r="E9">
-        <v>700.4</v>
+        <v>710.6199999999999</v>
       </c>
       <c r="F9">
-        <v>21.4</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>15.9</v>
+        <v>17.2</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D10">
-        <v>104.8866666666667</v>
+        <v>112.2857142857143</v>
       </c>
       <c r="E10">
-        <v>629.3199999999999</v>
+        <v>786</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>9.5</v>
       </c>
       <c r="G10">
-        <v>21.6</v>
+        <v>23.7</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3075,28 +3140,28 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D11">
-        <v>113.3966666666667</v>
+        <v>110.1485714285714</v>
       </c>
       <c r="E11">
-        <v>680.38</v>
+        <v>771.04</v>
       </c>
       <c r="F11">
-        <v>7.8</v>
+        <v>2.7</v>
       </c>
       <c r="G11">
-        <v>45.2</v>
+        <v>54.90000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3114,16 +3179,16 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3134,16 +3199,16 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3151,19 +3216,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>55</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3171,19 +3236,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3191,19 +3256,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3211,19 +3276,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3231,19 +3296,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3251,19 +3316,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3271,19 +3336,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3294,16 +3359,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
         <v>-12</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3314,16 +3379,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11">
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3333,33 +3398,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>106</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -3381,193 +3449,217 @@
       <c r="G2">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>-2</v>
+      </c>
+      <c r="E3">
+        <v>-10</v>
+      </c>
+      <c r="F3">
+        <v>-8</v>
+      </c>
+      <c r="G3">
+        <v>-4</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
         <v>-1</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>7</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>-4</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>-2</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>11</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>12</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
-      <c r="H5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>-2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>-1</v>
+      </c>
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
         <v>-1</v>
       </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>-1</v>
-      </c>
-      <c r="C8">
+      <c r="C9">
         <v>-6</v>
-      </c>
-      <c r="D8">
-        <v>-2</v>
-      </c>
-      <c r="E8">
-        <v>-6</v>
-      </c>
-      <c r="F8">
-        <v>-5</v>
-      </c>
-      <c r="G8">
-        <v>-2</v>
-      </c>
-      <c r="H8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
       </c>
       <c r="D9">
         <v>-2</v>
       </c>
       <c r="E9">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="F9">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="G9">
-        <v>-4</v>
-      </c>
-      <c r="H9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>-2</v>
+      </c>
+      <c r="H9">
+        <v>-7</v>
+      </c>
+      <c r="I9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -3589,11 +3681,14 @@
       <c r="G10">
         <v>-12</v>
       </c>
-      <c r="H10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10">
+        <v>-12</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -3615,8 +3710,11 @@
       <c r="G11">
         <v>-13</v>
       </c>
-      <c r="H11" t="s">
-        <v>98</v>
+      <c r="H11">
+        <v>-16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
+++ b/data/leagues/Campers and Skiers and Prahlad 2026.xlsx
@@ -241,34 +241,34 @@
     <t>1-6</t>
   </si>
   <si>
-    <t>11.3-2.7-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.4-0.1</t>
-  </si>
-  <si>
-    <t>8.0-6.0-0.1</t>
+    <t>11.2-2.8-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.4-0.1</t>
+  </si>
+  <si>
+    <t>7.9-6.0-0.1</t>
   </si>
   <si>
     <t>7.3-6.6-0.1</t>
   </si>
   <si>
-    <t>7.5-6.4-0.1</t>
+    <t>7.6-6.3-0.1</t>
   </si>
   <si>
     <t>7.4-6.5-0.1</t>
   </si>
   <si>
-    <t>6.1-7.8-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.7-0.1</t>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
   </si>
   <si>
     <t>4.6-9.3-0.1</t>
   </si>
   <si>
-    <t>3.7-10.2-0.1</t>
+    <t>3.8-10.2-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -1808,22 +1808,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>93.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="C2">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="D2">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="E2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1846,37 +1846,37 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="C3">
-        <v>34.8</v>
+        <v>35.2</v>
       </c>
       <c r="D3">
-        <v>23.4</v>
+        <v>19.4</v>
       </c>
       <c r="E3">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="F3">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="G3">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="H3">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="I3">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1884,37 +1884,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="C4">
-        <v>24.1</v>
+        <v>20.3</v>
       </c>
       <c r="D4">
-        <v>19.3</v>
+        <v>23.5</v>
       </c>
       <c r="E4">
-        <v>20.1</v>
+        <v>18.6</v>
       </c>
       <c r="F4">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="G4">
-        <v>10.4</v>
+        <v>11.9</v>
       </c>
       <c r="H4">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J4">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>91.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1925,34 +1925,34 @@
         <v>0.7</v>
       </c>
       <c r="C5">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="D5">
-        <v>18.9</v>
+        <v>17.6</v>
       </c>
       <c r="E5">
-        <v>19.1</v>
+        <v>20.6</v>
       </c>
       <c r="F5">
-        <v>18.5</v>
+        <v>19.2</v>
       </c>
       <c r="G5">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J5">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K5">
         <v>0.1</v>
       </c>
       <c r="L5">
-        <v>86.3</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1960,37 +1960,37 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="C6">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="D6">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="E6">
-        <v>16.5</v>
+        <v>18.9</v>
       </c>
       <c r="F6">
-        <v>18.6</v>
+        <v>17.2</v>
       </c>
       <c r="G6">
-        <v>18.2</v>
+        <v>16.6</v>
       </c>
       <c r="H6">
         <v>9.5</v>
       </c>
       <c r="I6">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="K6">
         <v>0.2</v>
       </c>
       <c r="L6">
-        <v>84.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1998,37 +1998,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C7">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="D7">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="E7">
-        <v>19.8</v>
+        <v>16.2</v>
       </c>
       <c r="F7">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="G7">
-        <v>16.6</v>
+        <v>17.6</v>
       </c>
       <c r="H7">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="L7">
-        <v>78.2</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2039,34 +2039,34 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="D8">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="E8">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F8">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G8">
-        <v>18.3</v>
+        <v>19.6</v>
       </c>
       <c r="H8">
-        <v>27.5</v>
+        <v>28.9</v>
       </c>
       <c r="I8">
-        <v>18.8</v>
+        <v>17.3</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="K8">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2080,31 +2080,31 @@
         <v>0.1</v>
       </c>
       <c r="D9">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="G9">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="H9">
-        <v>14.2</v>
+        <v>12.7</v>
       </c>
       <c r="I9">
-        <v>27.9</v>
+        <v>25.1</v>
       </c>
       <c r="J9">
-        <v>27.7</v>
+        <v>31.2</v>
       </c>
       <c r="K9">
-        <v>17.2</v>
+        <v>19</v>
       </c>
       <c r="L9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2115,34 +2115,34 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E10">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F10">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G10">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H10">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="I10">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="J10">
-        <v>29.5</v>
+        <v>29.1</v>
       </c>
       <c r="K10">
-        <v>23.7</v>
+        <v>22.7</v>
       </c>
       <c r="L10">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2162,25 +2162,25 @@
         <v>0.2</v>
       </c>
       <c r="F11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="I11">
-        <v>12.8</v>
+        <v>16.2</v>
       </c>
       <c r="J11">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="K11">
-        <v>54.9</v>
+        <v>52.6</v>
       </c>
       <c r="L11">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>
@@ -2227,19 +2227,19 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>92.80000000000001</v>
+        <v>92.10000000000001</v>
       </c>
       <c r="D2">
-        <v>99.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="F2">
         <v>99.90000000000001</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -2253,28 +2253,28 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>82.3</v>
+        <v>80.10000000000001</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>98</v>
+        <v>99.2</v>
       </c>
       <c r="E3">
-        <v>97.39999999999999</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="F3">
         <v>95.3</v>
       </c>
       <c r="G3">
-        <v>93.40000000000001</v>
+        <v>93.89999999999999</v>
       </c>
       <c r="H3">
-        <v>97.39999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I3">
-        <v>97.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2282,28 +2282,28 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>99.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C4">
-        <v>90.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D4">
-        <v>57.09999999999999</v>
+        <v>57.59999999999999</v>
       </c>
       <c r="E4">
-        <v>24.4</v>
+        <v>25.7</v>
       </c>
       <c r="F4">
-        <v>41.6</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>66.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H4">
-        <v>90.60000000000001</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="I4">
-        <v>93.10000000000001</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2311,19 +2311,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>99.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C5">
-        <v>79.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D5">
-        <v>81</v>
+        <v>81.10000000000001</v>
       </c>
       <c r="E5">
-        <v>60.4</v>
+        <v>58.59999999999999</v>
       </c>
       <c r="F5">
-        <v>66.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G5">
         <v>94.19999999999999</v>
@@ -2332,7 +2332,7 @@
         <v>87.40000000000001</v>
       </c>
       <c r="I5">
-        <v>84.8</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2340,28 +2340,28 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="C6">
-        <v>90.10000000000001</v>
+        <v>91</v>
       </c>
       <c r="D6">
-        <v>94.09999999999999</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="E6">
-        <v>87.3</v>
+        <v>88</v>
       </c>
       <c r="F6">
-        <v>97.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G6">
-        <v>97.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="H6">
-        <v>84.8</v>
+        <v>84.5</v>
       </c>
       <c r="I6">
-        <v>83.09999999999999</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2369,28 +2369,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="C7">
-        <v>27.3</v>
+        <v>25.2</v>
       </c>
       <c r="D7">
-        <v>64.7</v>
+        <v>65.10000000000001</v>
       </c>
       <c r="E7">
-        <v>82.69999999999999</v>
+        <v>85.39999999999999</v>
       </c>
       <c r="F7">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="G7">
-        <v>69.3</v>
+        <v>68.10000000000001</v>
       </c>
       <c r="H7">
-        <v>78.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I7">
-        <v>78.5</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2398,28 +2398,28 @@
         <v>0</v>
       </c>
       <c r="B8">
-        <v>31.5</v>
+        <v>30.1</v>
       </c>
       <c r="C8">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="D8">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="E8">
-        <v>25.9</v>
+        <v>25.1</v>
       </c>
       <c r="F8">
-        <v>56.39999999999999</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="G8">
-        <v>27.3</v>
+        <v>28.1</v>
       </c>
       <c r="H8">
-        <v>40.7</v>
+        <v>39.1</v>
       </c>
       <c r="I8">
-        <v>39.8</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2427,28 +2427,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>53.40000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="C9">
-        <v>5.3</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
-        <v>19.8</v>
+        <v>17.5</v>
       </c>
       <c r="F9">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="G9">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="H9">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>11.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2456,28 +2456,28 @@
         <v>3</v>
       </c>
       <c r="B10">
-        <v>31.6</v>
+        <v>33.2</v>
       </c>
       <c r="C10">
-        <v>94.39999999999999</v>
+        <v>94.69999999999999</v>
       </c>
       <c r="D10">
-        <v>70.8</v>
+        <v>68.2</v>
       </c>
       <c r="E10">
-        <v>90.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F10">
-        <v>36</v>
+        <v>34.7</v>
       </c>
       <c r="G10">
-        <v>27.6</v>
+        <v>29.8</v>
       </c>
       <c r="H10">
+        <v>10.3</v>
+      </c>
+      <c r="I10">
         <v>8.699999999999999</v>
-      </c>
-      <c r="I10">
-        <v>9.700000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2488,25 +2488,25 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="D11">
-        <v>33.6</v>
+        <v>32.7</v>
       </c>
       <c r="E11">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="F11">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="G11">
-        <v>5.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="H11">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>
@@ -2920,7 +2920,7 @@
         <v>857.0799999999999</v>
       </c>
       <c r="F3">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2949,10 +2949,10 @@
         <v>861.66</v>
       </c>
       <c r="F4">
-        <v>91.40000000000001</v>
+        <v>92.10000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
         <v>74</v>
@@ -2978,7 +2978,7 @@
         <v>904.8</v>
       </c>
       <c r="F5">
-        <v>86.3</v>
+        <v>87.2</v>
       </c>
       <c r="G5">
         <v>0.1</v>
@@ -3007,7 +3007,7 @@
         <v>841.0600000000001</v>
       </c>
       <c r="F6">
-        <v>84.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G6">
         <v>0.2</v>
@@ -3016,7 +3016,7 @@
         <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3036,10 +3036,10 @@
         <v>822.16</v>
       </c>
       <c r="F7">
-        <v>78.2</v>
+        <v>77.2</v>
       </c>
       <c r="G7">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="s">
         <v>77</v>
@@ -3065,10 +3065,10 @@
         <v>801.64</v>
       </c>
       <c r="F8">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="G8">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="H8" t="s">
         <v>78</v>
@@ -3094,10 +3094,10 @@
         <v>710.6199999999999</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>17.2</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
         <v>79</v>
@@ -3123,10 +3123,10 @@
         <v>786</v>
       </c>
       <c r="F10">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>23.7</v>
+        <v>22.7</v>
       </c>
       <c r="H10" t="s">
         <v>80</v>
@@ -3152,10 +3152,10 @@
         <v>771.04</v>
       </c>
       <c r="F11">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G11">
-        <v>54.90000000000001</v>
+        <v>52.6</v>
       </c>
       <c r="H11" t="s">
         <v>81</v>
